--- a/data/export/2026-10-13-operations.xlsx
+++ b/data/export/2026-10-13-operations.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD15"/>
+  <dimension ref="A1:AD25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -442,7 +442,7 @@
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="18" customWidth="1" min="11" max="11"/>
     <col width="26" customWidth="1" min="12" max="12"/>
-    <col width="18" customWidth="1" min="13" max="13"/>
+    <col width="25" customWidth="1" min="13" max="13"/>
     <col width="22" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
@@ -676,7 +676,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>05:50</t>
+          <t>06:22</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -726,7 +726,7 @@
       <c r="AC2" s="2" t="inlineStr"/>
       <c r="AD2" s="2" t="inlineStr">
         <is>
-          <t>—/5</t>
+          <t>—/9</t>
         </is>
       </c>
     </row>
@@ -792,7 +792,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>05:50</t>
+          <t>06:22</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       <c r="AC3" s="2" t="inlineStr"/>
       <c r="AD3" s="2" t="inlineStr">
         <is>
-          <t>—/5</t>
+          <t>—/9</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>05:50</t>
+          <t>06:22</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -958,7 +958,7 @@
       <c r="AC4" s="2" t="inlineStr"/>
       <c r="AD4" s="2" t="inlineStr">
         <is>
-          <t>—/5</t>
+          <t>—/9</t>
         </is>
       </c>
     </row>
@@ -971,22 +971,22 @@
       <c r="B5" s="2" t="inlineStr"/>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>沪A67983D</t>
+          <t>沪A67026D</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>06:35</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
           <t>金杨路金口路</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>06:35</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1024,7 +1024,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>05:50</t>
+          <t>06:22</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -1074,7 +1074,7 @@
       <c r="AC5" s="2" t="inlineStr"/>
       <c r="AD5" s="2" t="inlineStr">
         <is>
-          <t>—/5</t>
+          <t>—/9</t>
         </is>
       </c>
     </row>
@@ -1087,7 +1087,7 @@
       <c r="B6" s="2" t="inlineStr"/>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>沪A13735A</t>
+          <t>沪A67983D</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -1097,7 +1097,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>06:55</t>
+          <t>06:35</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -1140,7 +1140,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>05:50</t>
+          <t>06:22</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1154,7 +1154,7 @@
       <c r="U6" s="2" t="inlineStr"/>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>06:55</t>
+          <t>06:35</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
@@ -1190,35 +1190,35 @@
       <c r="AC6" s="2" t="inlineStr"/>
       <c r="AD6" s="2" t="inlineStr">
         <is>
-          <t>—/5</t>
+          <t>—/9</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr"/>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>沪A09172D</t>
+          <t>沪A68870D</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>05:50</t>
+          <t>06:48</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1251,12 +1251,12 @@
       <c r="N7" s="2" t="inlineStr"/>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>05:49</t>
+          <t>06:12</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>05:49</t>
+          <t>06:22</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1270,7 +1270,7 @@
       <c r="U7" s="2" t="inlineStr"/>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>05:50</t>
+          <t>06:48</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -1306,35 +1306,35 @@
       <c r="AC7" s="2" t="inlineStr"/>
       <c r="AD7" s="2" t="inlineStr">
         <is>
-          <t>—/6</t>
+          <t>—/9</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr"/>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>沪A62880D</t>
+          <t>沪A13735A</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>05:50</t>
+          <t>06:55</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1367,12 +1367,12 @@
       <c r="N8" s="2" t="inlineStr"/>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>05:49</t>
+          <t>05:50</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>05:49</t>
+          <t>06:22</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1386,7 +1386,7 @@
       <c r="U8" s="2" t="inlineStr"/>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>05:50</t>
+          <t>06:55</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1422,35 +1422,35 @@
       <c r="AC8" s="2" t="inlineStr"/>
       <c r="AD8" s="2" t="inlineStr">
         <is>
-          <t>—/6</t>
+          <t>—/9</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr"/>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>沪A57051D</t>
+          <t>沪A32899D</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1483,12 +1483,12 @@
       <c r="N9" s="2" t="inlineStr"/>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>05:49</t>
+          <t>06:22</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>05:49</t>
+          <t>06:22</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1502,7 +1502,7 @@
       <c r="U9" s="2" t="inlineStr"/>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
@@ -1538,35 +1538,35 @@
       <c r="AC9" s="2" t="inlineStr"/>
       <c r="AD9" s="2" t="inlineStr">
         <is>
-          <t>—/6</t>
+          <t>—/9</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr"/>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>沪A66883D</t>
+          <t>沪A67353D</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:15</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       <c r="N10" s="2" t="inlineStr"/>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>05:49</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>05:49</t>
+          <t>06:22</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1618,7 +1618,7 @@
       <c r="U10" s="2" t="inlineStr"/>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:15</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -1654,7 +1654,7 @@
       <c r="AC10" s="2" t="inlineStr"/>
       <c r="AD10" s="2" t="inlineStr">
         <is>
-          <t>—/6</t>
+          <t>—/9</t>
         </is>
       </c>
     </row>
@@ -1667,7 +1667,7 @@
       <c r="B11" s="2" t="inlineStr"/>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>沪A51682D</t>
+          <t>沪A09172D</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1677,7 +1677,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>05:50</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1687,32 +1687,36 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:03</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr"/>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
           <t>05:49</t>
@@ -1720,7 +1724,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>05:49</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1734,7 +1738,7 @@
       <c r="U11" s="2" t="inlineStr"/>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>05:50</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1744,17 +1748,17 @@
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
@@ -1764,13 +1768,17 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC11" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC11" s="2" t="inlineStr">
+        <is>
+          <t>133.0</t>
+        </is>
+      </c>
       <c r="AD11" s="2" t="inlineStr">
         <is>
-          <t>—/6</t>
+          <t>1/10</t>
         </is>
       </c>
     </row>
@@ -1783,7 +1791,7 @@
       <c r="B12" s="2" t="inlineStr"/>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>沪A71572D</t>
+          <t>沪A62880D</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -1793,7 +1801,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>05:50</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1803,32 +1811,36 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:05</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>135分钟</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr"/>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
           <t>05:49</t>
@@ -1836,7 +1848,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>05:49</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1850,7 +1862,7 @@
       <c r="U12" s="2" t="inlineStr"/>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>05:50</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
@@ -1860,17 +1872,17 @@
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
@@ -1880,41 +1892,45 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC12" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC12" s="2" t="inlineStr">
+        <is>
+          <t>135.0</t>
+        </is>
+      </c>
       <c r="AD12" s="2" t="inlineStr">
         <is>
-          <t>—/6</t>
+          <t>2/10</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr"/>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A57051D</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>05:58</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1947,12 +1963,12 @@
       <c r="N13" s="2" t="inlineStr"/>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>05:48</t>
+          <t>05:49</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>05:48</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1966,7 +1982,7 @@
       <c r="U13" s="2" t="inlineStr"/>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>05:58</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -2002,25 +2018,25 @@
       <c r="AC13" s="2" t="inlineStr"/>
       <c r="AD13" s="2" t="inlineStr">
         <is>
-          <t>—/3</t>
+          <t>—/10</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr"/>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>沪A35616D</t>
+          <t>沪A66883D</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -2030,7 +2046,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2063,12 +2079,12 @@
       <c r="N14" s="2" t="inlineStr"/>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>05:48</t>
+          <t>05:49</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>05:48</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2118,35 +2134,35 @@
       <c r="AC14" s="2" t="inlineStr"/>
       <c r="AD14" s="2" t="inlineStr">
         <is>
-          <t>—/3</t>
+          <t>—/10</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr"/>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>沪A57022D</t>
+          <t>沪A51682D</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>06:26</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2179,12 +2195,12 @@
       <c r="N15" s="2" t="inlineStr"/>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>05:48</t>
+          <t>05:49</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>05:48</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2198,7 +2214,7 @@
       <c r="U15" s="2" t="inlineStr"/>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>06:26</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
@@ -2234,7 +2250,1183 @@
       <c r="AC15" s="2" t="inlineStr"/>
       <c r="AD15" s="2" t="inlineStr">
         <is>
-          <t>—/3</t>
+          <t>—/10</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr"/>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>沪A71572D</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr"/>
+      <c r="L16" s="2" t="inlineStr"/>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr"/>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>05:49</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr"/>
+      <c r="S16" s="2" t="inlineStr"/>
+      <c r="T16" s="2" t="inlineStr"/>
+      <c r="U16" s="2" t="inlineStr"/>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="W16" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X16" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z16" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC16" s="2" t="inlineStr"/>
+      <c r="AD16" s="2" t="inlineStr">
+        <is>
+          <t>—/10</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr"/>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>沪A11062A</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>06:36</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr"/>
+      <c r="L17" s="2" t="inlineStr"/>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr"/>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr"/>
+      <c r="S17" s="2" t="inlineStr"/>
+      <c r="T17" s="2" t="inlineStr"/>
+      <c r="U17" s="2" t="inlineStr"/>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>06:36</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X17" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z17" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC17" s="2" t="inlineStr"/>
+      <c r="AD17" s="2" t="inlineStr">
+        <is>
+          <t>—/10</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr"/>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>沪A37823D</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr"/>
+      <c r="L18" s="2" t="inlineStr"/>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr"/>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R18" s="2" t="inlineStr"/>
+      <c r="S18" s="2" t="inlineStr"/>
+      <c r="T18" s="2" t="inlineStr"/>
+      <c r="U18" s="2" t="inlineStr"/>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="W18" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X18" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z18" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB18" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC18" s="2" t="inlineStr"/>
+      <c r="AD18" s="2" t="inlineStr">
+        <is>
+          <t>—/10</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr"/>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>沪A70597D</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr"/>
+      <c r="L19" s="2" t="inlineStr"/>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr"/>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr"/>
+      <c r="S19" s="2" t="inlineStr"/>
+      <c r="T19" s="2" t="inlineStr"/>
+      <c r="U19" s="2" t="inlineStr"/>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="W19" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X19" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z19" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC19" s="2" t="inlineStr"/>
+      <c r="AD19" s="2" t="inlineStr">
+        <is>
+          <t>—/10</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr"/>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>沪A95621D</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr"/>
+      <c r="L20" s="2" t="inlineStr"/>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr"/>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr"/>
+      <c r="S20" s="2" t="inlineStr"/>
+      <c r="T20" s="2" t="inlineStr"/>
+      <c r="U20" s="2" t="inlineStr"/>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="W20" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X20" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z20" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC20" s="2" t="inlineStr"/>
+      <c r="AD20" s="2" t="inlineStr">
+        <is>
+          <t>—/10</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr"/>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>05:58</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>07:22</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>84分钟</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr"/>
+      <c r="L21" s="2" t="inlineStr"/>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>05:48</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R21" s="2" t="inlineStr"/>
+      <c r="S21" s="2" t="inlineStr"/>
+      <c r="T21" s="2" t="inlineStr"/>
+      <c r="U21" s="2" t="inlineStr"/>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>05:58</t>
+        </is>
+      </c>
+      <c r="W21" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X21" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y21" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z21" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB21" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC21" s="2" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="AD21" s="2" t="inlineStr">
+        <is>
+          <t>1/5</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr"/>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>07:36</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>86分钟</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr"/>
+      <c r="L22" s="2" t="inlineStr"/>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>05:48</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr"/>
+      <c r="S22" s="2" t="inlineStr"/>
+      <c r="T22" s="2" t="inlineStr"/>
+      <c r="U22" s="2" t="inlineStr"/>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="W22" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X22" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y22" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z22" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC22" s="2" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
+      <c r="AD22" s="2" t="inlineStr">
+        <is>
+          <t>2/5</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr"/>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>06:25</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr"/>
+      <c r="L23" s="2" t="inlineStr"/>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr"/>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>05:48</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr"/>
+      <c r="S23" s="2" t="inlineStr"/>
+      <c r="T23" s="2" t="inlineStr"/>
+      <c r="U23" s="2" t="inlineStr"/>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>06:25</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X23" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z23" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC23" s="2" t="inlineStr"/>
+      <c r="AD23" s="2" t="inlineStr">
+        <is>
+          <t>—/5</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr"/>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr"/>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr"/>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R24" s="2" t="inlineStr"/>
+      <c r="S24" s="2" t="inlineStr"/>
+      <c r="T24" s="2" t="inlineStr"/>
+      <c r="U24" s="2" t="inlineStr"/>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="W24" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X24" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z24" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC24" s="2" t="inlineStr"/>
+      <c r="AD24" s="2" t="inlineStr">
+        <is>
+          <t>—/5</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr"/>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr"/>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr"/>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr"/>
+      <c r="S25" s="2" t="inlineStr"/>
+      <c r="T25" s="2" t="inlineStr"/>
+      <c r="U25" s="2" t="inlineStr"/>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X25" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z25" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC25" s="2" t="inlineStr"/>
+      <c r="AD25" s="2" t="inlineStr">
+        <is>
+          <t>—/5</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-13-operations.xlsx
+++ b/data/export/2026-10-13-operations.xlsx
@@ -427,13 +427,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD25"/>
+  <dimension ref="A1:AD54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
@@ -643,32 +643,36 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:17</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr"/>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
           <t>05:50</t>
@@ -676,7 +680,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -700,33 +704,37 @@
       </c>
       <c r="X2" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB2" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC2" s="2" t="inlineStr"/>
+      <c r="AC2" s="2" t="inlineStr">
+        <is>
+          <t>72.0</t>
+        </is>
+      </c>
       <c r="AD2" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>1/13</t>
         </is>
       </c>
     </row>
@@ -759,32 +767,36 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr"/>
       <c r="L3" s="2" t="inlineStr"/>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
           <t>05:50</t>
@@ -792,7 +804,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -816,17 +828,17 @@
       </c>
       <c r="X3" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
@@ -836,13 +848,17 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC3" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC3" s="2" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
+      </c>
       <c r="AD3" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>2/13</t>
         </is>
       </c>
     </row>
@@ -875,32 +891,36 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:41</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr"/>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
           <t>05:50</t>
@@ -908,7 +928,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -932,33 +952,37 @@
       </c>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC4" s="2" t="inlineStr"/>
+      <c r="AC4" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
       <c r="AD4" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>3/13</t>
         </is>
       </c>
     </row>
@@ -1024,7 +1048,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -1063,7 +1087,7 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
@@ -1074,7 +1098,7 @@
       <c r="AC5" s="2" t="inlineStr"/>
       <c r="AD5" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
@@ -1107,32 +1131,36 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:56</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr"/>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
           <t>05:50</t>
@@ -1140,7 +1168,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1164,17 +1192,17 @@
       </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
@@ -1184,13 +1212,17 @@
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC6" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC6" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
       <c r="AD6" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>3/13</t>
         </is>
       </c>
     </row>
@@ -1256,7 +1288,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1306,7 +1338,7 @@
       <c r="AC7" s="2" t="inlineStr"/>
       <c r="AD7" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
@@ -1372,7 +1404,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1422,7 +1454,7 @@
       <c r="AC8" s="2" t="inlineStr"/>
       <c r="AD8" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
@@ -1488,7 +1520,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1538,7 +1570,7 @@
       <c r="AC9" s="2" t="inlineStr"/>
       <c r="AD9" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
@@ -1551,22 +1583,22 @@
       <c r="B10" s="2" t="inlineStr"/>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>沪A67353D</t>
+          <t>沪A66513D</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>金杨路金口路</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>07:15</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1599,12 +1631,12 @@
       <c r="N10" s="2" t="inlineStr"/>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>06:02</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1618,7 +1650,7 @@
       <c r="U10" s="2" t="inlineStr"/>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -1654,77 +1686,73 @@
       <c r="AC10" s="2" t="inlineStr"/>
       <c r="AD10" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr"/>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>沪A09172D</t>
+          <t>沪A67353D</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>05:50</t>
+          <t>07:15</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>08:03</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>133分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr"/>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr"/>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>05:49</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1738,7 +1766,7 @@
       <c r="U11" s="2" t="inlineStr"/>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>05:50</t>
+          <t>07:15</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1748,17 +1776,17 @@
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y11" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
@@ -1768,87 +1796,79 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC11" s="2" t="inlineStr">
-        <is>
-          <t>133.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC11" s="2" t="inlineStr"/>
       <c r="AD11" s="2" t="inlineStr">
         <is>
-          <t>1/10</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr"/>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>沪A62880D</t>
+          <t>沪A31073D</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>05:50</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>08:05</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>135分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr"/>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr"/>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>05:49</t>
+          <t>05:50</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1862,7 +1882,7 @@
       <c r="U12" s="2" t="inlineStr"/>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>05:50</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
@@ -1872,17 +1892,17 @@
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y12" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
@@ -1892,45 +1912,41 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC12" s="2" t="inlineStr">
-        <is>
-          <t>135.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC12" s="2" t="inlineStr"/>
       <c r="AD12" s="2" t="inlineStr">
         <is>
-          <t>2/10</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr"/>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>沪A57051D</t>
+          <t>沪A32298D</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:35</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1963,12 +1979,12 @@
       <c r="N13" s="2" t="inlineStr"/>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>05:49</t>
+          <t>05:50</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1982,7 +1998,7 @@
       <c r="U13" s="2" t="inlineStr"/>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:35</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -2007,46 +2023,50 @@
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC13" s="2" t="inlineStr"/>
+      <c r="AC13" s="2" t="inlineStr">
+        <is>
+          <t>72.0</t>
+        </is>
+      </c>
       <c r="AD13" s="2" t="inlineStr">
         <is>
-          <t>—/10</t>
+          <t>1/13</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr"/>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>沪A66883D</t>
+          <t>沪A35717D</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:36</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2079,12 +2099,12 @@
       <c r="N14" s="2" t="inlineStr"/>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>05:49</t>
+          <t>07:02</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2098,7 +2118,7 @@
       <c r="U14" s="2" t="inlineStr"/>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:36</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2134,35 +2154,35 @@
       <c r="AC14" s="2" t="inlineStr"/>
       <c r="AD14" s="2" t="inlineStr">
         <is>
-          <t>—/10</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr"/>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>沪A51682D</t>
+          <t>沪A02126A</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>07:48</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2195,12 +2215,12 @@
       <c r="N15" s="2" t="inlineStr"/>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>05:49</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2214,7 +2234,7 @@
       <c r="U15" s="2" t="inlineStr"/>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>07:48</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
@@ -2250,35 +2270,35 @@
       <c r="AC15" s="2" t="inlineStr"/>
       <c r="AD15" s="2" t="inlineStr">
         <is>
-          <t>—/10</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr"/>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>沪A71572D</t>
+          <t>沪A68397D</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:55</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2311,12 +2331,12 @@
       <c r="N16" s="2" t="inlineStr"/>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>05:49</t>
+          <t>05:50</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2330,7 +2350,7 @@
       <c r="U16" s="2" t="inlineStr"/>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:55</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -2355,46 +2375,50 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB16" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC16" s="2" t="inlineStr"/>
+      <c r="AC16" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
       <c r="AD16" s="2" t="inlineStr">
         <is>
-          <t>—/10</t>
+          <t>3/13</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr"/>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>沪A11062A</t>
+          <t>沪A67026D</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2427,12 +2451,12 @@
       <c r="N17" s="2" t="inlineStr"/>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>05:50</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2446,7 +2470,7 @@
       <c r="U17" s="2" t="inlineStr"/>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2471,7 +2495,7 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
@@ -2482,7 +2506,7 @@
       <c r="AC17" s="2" t="inlineStr"/>
       <c r="AD17" s="2" t="inlineStr">
         <is>
-          <t>—/10</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
@@ -2495,7 +2519,7 @@
       <c r="B18" s="2" t="inlineStr"/>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>沪A37823D</t>
+          <t>沪A09172D</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -2505,7 +2529,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>05:50</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -2515,40 +2539,44 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr"/>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>05:49</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2562,7 +2590,7 @@
       <c r="U18" s="2" t="inlineStr"/>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>05:50</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
@@ -2572,17 +2600,17 @@
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
@@ -2592,13 +2620,17 @@
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC18" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC18" s="2" t="inlineStr">
+        <is>
+          <t>131.0</t>
+        </is>
+      </c>
       <c r="AD18" s="2" t="inlineStr">
         <is>
-          <t>—/10</t>
+          <t>1/20</t>
         </is>
       </c>
     </row>
@@ -2611,7 +2643,7 @@
       <c r="B19" s="2" t="inlineStr"/>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>沪A70597D</t>
+          <t>沪A62880D</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -2621,7 +2653,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>05:50</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -2631,40 +2663,44 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:05</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>135分钟</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr"/>
       <c r="L19" s="2" t="inlineStr"/>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>05:49</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2678,7 +2714,7 @@
       <c r="U19" s="2" t="inlineStr"/>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>05:50</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -2688,17 +2724,17 @@
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
@@ -2708,13 +2744,17 @@
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC19" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC19" s="2" t="inlineStr">
+        <is>
+          <t>135.0</t>
+        </is>
+      </c>
       <c r="AD19" s="2" t="inlineStr">
         <is>
-          <t>—/10</t>
+          <t>2/20</t>
         </is>
       </c>
     </row>
@@ -2727,22 +2767,22 @@
       <c r="B20" s="2" t="inlineStr"/>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>沪A95621D</t>
+          <t>沪A57051D</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>06:54</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2775,12 +2815,12 @@
       <c r="N20" s="2" t="inlineStr"/>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>05:49</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2794,7 +2834,7 @@
       <c r="U20" s="2" t="inlineStr"/>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2830,77 +2870,73 @@
       <c r="AC20" s="2" t="inlineStr"/>
       <c r="AD20" s="2" t="inlineStr">
         <is>
-          <t>—/10</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr"/>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A66883D</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>05:58</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>84分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr"/>
       <c r="L21" s="2" t="inlineStr"/>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr"/>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>05:48</t>
+          <t>05:49</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2914,7 +2950,7 @@
       <c r="U21" s="2" t="inlineStr"/>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>05:58</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
@@ -2924,17 +2960,17 @@
       </c>
       <c r="X21" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y21" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
@@ -2944,87 +2980,79 @@
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC21" s="2" t="inlineStr">
-        <is>
-          <t>84.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC21" s="2" t="inlineStr"/>
       <c r="AD21" s="2" t="inlineStr">
         <is>
-          <t>1/5</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr"/>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>沪A35616D</t>
+          <t>沪A51682D</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>06:26</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>07:36</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>86分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr"/>
       <c r="L22" s="2" t="inlineStr"/>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr"/>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>05:48</t>
+          <t>05:49</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -3038,7 +3066,7 @@
       <c r="U22" s="2" t="inlineStr"/>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>06:26</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -3048,17 +3076,17 @@
       </c>
       <c r="X22" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y22" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
@@ -3068,45 +3096,41 @@
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC22" s="2" t="inlineStr">
-        <is>
-          <t>86.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC22" s="2" t="inlineStr"/>
       <c r="AD22" s="2" t="inlineStr">
         <is>
-          <t>2/5</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr"/>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>沪A57022D</t>
+          <t>沪A71572D</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3139,12 +3163,12 @@
       <c r="N23" s="2" t="inlineStr"/>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>05:48</t>
+          <t>05:49</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -3158,7 +3182,7 @@
       <c r="U23" s="2" t="inlineStr"/>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3194,35 +3218,35 @@
       <c r="AC23" s="2" t="inlineStr"/>
       <c r="AD23" s="2" t="inlineStr">
         <is>
-          <t>—/5</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr"/>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>沪A36809D</t>
+          <t>沪A11062A</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>06:36</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3260,7 +3284,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3274,7 +3298,7 @@
       <c r="U24" s="2" t="inlineStr"/>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>06:36</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
@@ -3310,35 +3334,35 @@
       <c r="AC24" s="2" t="inlineStr"/>
       <c r="AD24" s="2" t="inlineStr">
         <is>
-          <t>—/5</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr"/>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>沪A35172D</t>
+          <t>沪A37823D</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3371,12 +3395,12 @@
       <c r="N25" s="2" t="inlineStr"/>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3390,7 +3414,7 @@
       <c r="U25" s="2" t="inlineStr"/>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -3426,7 +3450,3371 @@
       <c r="AC25" s="2" t="inlineStr"/>
       <c r="AD25" s="2" t="inlineStr">
         <is>
-          <t>—/5</t>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr"/>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>沪A70597D</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr"/>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr"/>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr"/>
+      <c r="S26" s="2" t="inlineStr"/>
+      <c r="T26" s="2" t="inlineStr"/>
+      <c r="U26" s="2" t="inlineStr"/>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X26" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z26" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC26" s="2" t="inlineStr"/>
+      <c r="AD26" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr"/>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>沪A95621D</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr"/>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr"/>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R27" s="2" t="inlineStr"/>
+      <c r="S27" s="2" t="inlineStr"/>
+      <c r="T27" s="2" t="inlineStr"/>
+      <c r="U27" s="2" t="inlineStr"/>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="W27" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X27" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z27" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC27" s="2" t="inlineStr"/>
+      <c r="AD27" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr"/>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>沪A37267D</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>06:56</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr"/>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr"/>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr"/>
+      <c r="S28" s="2" t="inlineStr"/>
+      <c r="T28" s="2" t="inlineStr"/>
+      <c r="U28" s="2" t="inlineStr"/>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>06:56</t>
+        </is>
+      </c>
+      <c r="W28" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X28" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z28" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC28" s="2" t="inlineStr"/>
+      <c r="AD28" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr"/>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>沪A73927D</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr"/>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr"/>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr"/>
+      <c r="S29" s="2" t="inlineStr"/>
+      <c r="T29" s="2" t="inlineStr"/>
+      <c r="U29" s="2" t="inlineStr"/>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="W29" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X29" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z29" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB29" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC29" s="2" t="inlineStr"/>
+      <c r="AD29" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr"/>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>沪A55102D</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr"/>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr"/>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R30" s="2" t="inlineStr"/>
+      <c r="S30" s="2" t="inlineStr"/>
+      <c r="T30" s="2" t="inlineStr"/>
+      <c r="U30" s="2" t="inlineStr"/>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="W30" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X30" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z30" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB30" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC30" s="2" t="inlineStr"/>
+      <c r="AD30" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr"/>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>沪A36993D</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr"/>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr"/>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R31" s="2" t="inlineStr"/>
+      <c r="S31" s="2" t="inlineStr"/>
+      <c r="T31" s="2" t="inlineStr"/>
+      <c r="U31" s="2" t="inlineStr"/>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="W31" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X31" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z31" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC31" s="2" t="inlineStr"/>
+      <c r="AD31" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr"/>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>沪A67057D</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>07:26</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr"/>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr"/>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R32" s="2" t="inlineStr"/>
+      <c r="S32" s="2" t="inlineStr"/>
+      <c r="T32" s="2" t="inlineStr"/>
+      <c r="U32" s="2" t="inlineStr"/>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
+          <t>07:26</t>
+        </is>
+      </c>
+      <c r="W32" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X32" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z32" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB32" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC32" s="2" t="inlineStr"/>
+      <c r="AD32" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr"/>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>沪A72873D</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr"/>
+      <c r="L33" s="2" t="inlineStr"/>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr"/>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R33" s="2" t="inlineStr"/>
+      <c r="S33" s="2" t="inlineStr"/>
+      <c r="T33" s="2" t="inlineStr"/>
+      <c r="U33" s="2" t="inlineStr"/>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="W33" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X33" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z33" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB33" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC33" s="2" t="inlineStr"/>
+      <c r="AD33" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr"/>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>沪A67712D</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>07:41</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr"/>
+      <c r="L34" s="2" t="inlineStr"/>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr"/>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R34" s="2" t="inlineStr"/>
+      <c r="S34" s="2" t="inlineStr"/>
+      <c r="T34" s="2" t="inlineStr"/>
+      <c r="U34" s="2" t="inlineStr"/>
+      <c r="V34" s="2" t="inlineStr">
+        <is>
+          <t>07:41</t>
+        </is>
+      </c>
+      <c r="W34" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X34" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z34" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB34" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC34" s="2" t="inlineStr"/>
+      <c r="AD34" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr"/>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>沪A90275D</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr"/>
+      <c r="L35" s="2" t="inlineStr"/>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr"/>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R35" s="2" t="inlineStr"/>
+      <c r="S35" s="2" t="inlineStr"/>
+      <c r="T35" s="2" t="inlineStr"/>
+      <c r="U35" s="2" t="inlineStr"/>
+      <c r="V35" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="W35" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X35" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z35" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB35" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC35" s="2" t="inlineStr"/>
+      <c r="AD35" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr"/>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>沪A02891D</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr"/>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr"/>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R36" s="2" t="inlineStr"/>
+      <c r="S36" s="2" t="inlineStr"/>
+      <c r="T36" s="2" t="inlineStr"/>
+      <c r="U36" s="2" t="inlineStr"/>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="W36" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X36" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z36" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB36" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC36" s="2" t="inlineStr"/>
+      <c r="AD36" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr"/>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>沪A62981D</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr"/>
+      <c r="L37" s="2" t="inlineStr"/>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr"/>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R37" s="2" t="inlineStr"/>
+      <c r="S37" s="2" t="inlineStr"/>
+      <c r="T37" s="2" t="inlineStr"/>
+      <c r="U37" s="2" t="inlineStr"/>
+      <c r="V37" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="W37" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X37" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z37" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB37" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC37" s="2" t="inlineStr"/>
+      <c r="AD37" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr"/>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>05:58</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr"/>
+      <c r="L38" s="2" t="inlineStr"/>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr"/>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>05:48</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R38" s="2" t="inlineStr"/>
+      <c r="S38" s="2" t="inlineStr"/>
+      <c r="T38" s="2" t="inlineStr"/>
+      <c r="U38" s="2" t="inlineStr"/>
+      <c r="V38" s="2" t="inlineStr">
+        <is>
+          <t>05:58</t>
+        </is>
+      </c>
+      <c r="W38" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X38" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z38" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB38" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC38" s="2" t="inlineStr"/>
+      <c r="AD38" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr"/>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr"/>
+      <c r="L39" s="2" t="inlineStr"/>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr"/>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>05:48</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q39" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R39" s="2" t="inlineStr"/>
+      <c r="S39" s="2" t="inlineStr"/>
+      <c r="T39" s="2" t="inlineStr"/>
+      <c r="U39" s="2" t="inlineStr"/>
+      <c r="V39" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="W39" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X39" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z39" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB39" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC39" s="2" t="inlineStr"/>
+      <c r="AD39" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr"/>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>06:25</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr"/>
+      <c r="L40" s="2" t="inlineStr"/>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr"/>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>05:48</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R40" s="2" t="inlineStr"/>
+      <c r="S40" s="2" t="inlineStr"/>
+      <c r="T40" s="2" t="inlineStr"/>
+      <c r="U40" s="2" t="inlineStr"/>
+      <c r="V40" s="2" t="inlineStr">
+        <is>
+          <t>06:25</t>
+        </is>
+      </c>
+      <c r="W40" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X40" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z40" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB40" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC40" s="2" t="inlineStr"/>
+      <c r="AD40" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr"/>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr"/>
+      <c r="L41" s="2" t="inlineStr"/>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr"/>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R41" s="2" t="inlineStr"/>
+      <c r="S41" s="2" t="inlineStr"/>
+      <c r="T41" s="2" t="inlineStr"/>
+      <c r="U41" s="2" t="inlineStr"/>
+      <c r="V41" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="W41" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X41" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z41" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB41" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC41" s="2" t="inlineStr"/>
+      <c r="AD41" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr"/>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr"/>
+      <c r="L42" s="2" t="inlineStr"/>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr"/>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R42" s="2" t="inlineStr"/>
+      <c r="S42" s="2" t="inlineStr"/>
+      <c r="T42" s="2" t="inlineStr"/>
+      <c r="U42" s="2" t="inlineStr"/>
+      <c r="V42" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="W42" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X42" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z42" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB42" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC42" s="2" t="inlineStr"/>
+      <c r="AD42" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr"/>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr"/>
+      <c r="L43" s="2" t="inlineStr"/>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N43" s="2" t="inlineStr"/>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R43" s="2" t="inlineStr"/>
+      <c r="S43" s="2" t="inlineStr"/>
+      <c r="T43" s="2" t="inlineStr"/>
+      <c r="U43" s="2" t="inlineStr"/>
+      <c r="V43" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="W43" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X43" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z43" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB43" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC43" s="2" t="inlineStr"/>
+      <c r="AD43" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr"/>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr"/>
+      <c r="L44" s="2" t="inlineStr"/>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N44" s="2" t="inlineStr"/>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R44" s="2" t="inlineStr"/>
+      <c r="S44" s="2" t="inlineStr"/>
+      <c r="T44" s="2" t="inlineStr"/>
+      <c r="U44" s="2" t="inlineStr"/>
+      <c r="V44" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="W44" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X44" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z44" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB44" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC44" s="2" t="inlineStr"/>
+      <c r="AD44" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr"/>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr"/>
+      <c r="L45" s="2" t="inlineStr"/>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N45" s="2" t="inlineStr"/>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q45" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R45" s="2" t="inlineStr"/>
+      <c r="S45" s="2" t="inlineStr"/>
+      <c r="T45" s="2" t="inlineStr"/>
+      <c r="U45" s="2" t="inlineStr"/>
+      <c r="V45" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="W45" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X45" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z45" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB45" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC45" s="2" t="inlineStr"/>
+      <c r="AD45" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr"/>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr"/>
+      <c r="L46" s="2" t="inlineStr"/>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N46" s="2" t="inlineStr"/>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R46" s="2" t="inlineStr"/>
+      <c r="S46" s="2" t="inlineStr"/>
+      <c r="T46" s="2" t="inlineStr"/>
+      <c r="U46" s="2" t="inlineStr"/>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="W46" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X46" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z46" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB46" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC46" s="2" t="inlineStr"/>
+      <c r="AD46" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr"/>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="inlineStr"/>
+      <c r="L47" s="2" t="inlineStr"/>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N47" s="2" t="inlineStr"/>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q47" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R47" s="2" t="inlineStr"/>
+      <c r="S47" s="2" t="inlineStr"/>
+      <c r="T47" s="2" t="inlineStr"/>
+      <c r="U47" s="2" t="inlineStr"/>
+      <c r="V47" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="W47" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X47" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z47" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB47" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC47" s="2" t="inlineStr"/>
+      <c r="AD47" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr"/>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr"/>
+      <c r="L48" s="2" t="inlineStr"/>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N48" s="2" t="inlineStr"/>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q48" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R48" s="2" t="inlineStr"/>
+      <c r="S48" s="2" t="inlineStr"/>
+      <c r="T48" s="2" t="inlineStr"/>
+      <c r="U48" s="2" t="inlineStr"/>
+      <c r="V48" s="2" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="W48" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X48" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z48" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB48" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC48" s="2" t="inlineStr"/>
+      <c r="AD48" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr"/>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="inlineStr"/>
+      <c r="L49" s="2" t="inlineStr"/>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N49" s="2" t="inlineStr"/>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q49" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R49" s="2" t="inlineStr"/>
+      <c r="S49" s="2" t="inlineStr"/>
+      <c r="T49" s="2" t="inlineStr"/>
+      <c r="U49" s="2" t="inlineStr"/>
+      <c r="V49" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="W49" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X49" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z49" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB49" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC49" s="2" t="inlineStr"/>
+      <c r="AD49" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr"/>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr"/>
+      <c r="L50" s="2" t="inlineStr"/>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N50" s="2" t="inlineStr"/>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q50" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R50" s="2" t="inlineStr"/>
+      <c r="S50" s="2" t="inlineStr"/>
+      <c r="T50" s="2" t="inlineStr"/>
+      <c r="U50" s="2" t="inlineStr"/>
+      <c r="V50" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="W50" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X50" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z50" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB50" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC50" s="2" t="inlineStr"/>
+      <c r="AD50" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr"/>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K51" s="2" t="inlineStr"/>
+      <c r="L51" s="2" t="inlineStr"/>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N51" s="2" t="inlineStr"/>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>05:48</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q51" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R51" s="2" t="inlineStr"/>
+      <c r="S51" s="2" t="inlineStr"/>
+      <c r="T51" s="2" t="inlineStr"/>
+      <c r="U51" s="2" t="inlineStr"/>
+      <c r="V51" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="W51" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X51" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z51" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB51" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC51" s="2" t="inlineStr"/>
+      <c r="AD51" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr"/>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>沪A53629D</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K52" s="2" t="inlineStr"/>
+      <c r="L52" s="2" t="inlineStr"/>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N52" s="2" t="inlineStr"/>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q52" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R52" s="2" t="inlineStr"/>
+      <c r="S52" s="2" t="inlineStr"/>
+      <c r="T52" s="2" t="inlineStr"/>
+      <c r="U52" s="2" t="inlineStr"/>
+      <c r="V52" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="W52" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X52" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z52" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB52" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC52" s="2" t="inlineStr"/>
+      <c r="AD52" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr"/>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>07:45</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K53" s="2" t="inlineStr"/>
+      <c r="L53" s="2" t="inlineStr"/>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N53" s="2" t="inlineStr"/>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t>05:48</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q53" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R53" s="2" t="inlineStr"/>
+      <c r="S53" s="2" t="inlineStr"/>
+      <c r="T53" s="2" t="inlineStr"/>
+      <c r="U53" s="2" t="inlineStr"/>
+      <c r="V53" s="2" t="inlineStr">
+        <is>
+          <t>07:45</t>
+        </is>
+      </c>
+      <c r="W53" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X53" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z53" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB53" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC53" s="2" t="inlineStr"/>
+      <c r="AD53" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr"/>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>07:57</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="inlineStr"/>
+      <c r="L54" s="2" t="inlineStr"/>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N54" s="2" t="inlineStr"/>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>05:48</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q54" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R54" s="2" t="inlineStr"/>
+      <c r="S54" s="2" t="inlineStr"/>
+      <c r="T54" s="2" t="inlineStr"/>
+      <c r="U54" s="2" t="inlineStr"/>
+      <c r="V54" s="2" t="inlineStr">
+        <is>
+          <t>07:57</t>
+        </is>
+      </c>
+      <c r="W54" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X54" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z54" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB54" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC54" s="2" t="inlineStr"/>
+      <c r="AD54" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-13-operations.xlsx
+++ b/data/export/2026-10-13-operations.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD54"/>
+  <dimension ref="A1:AD82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -437,7 +437,7 @@
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="35" customWidth="1" min="8" max="8"/>
+    <col width="36" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="18" customWidth="1" min="11" max="11"/>
@@ -447,10 +447,10 @@
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
     <col width="10" customWidth="1" min="17" max="17"/>
-    <col width="10" customWidth="1" min="18" max="18"/>
+    <col width="16" customWidth="1" min="18" max="18"/>
     <col width="16" customWidth="1" min="19" max="19"/>
     <col width="20" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
+    <col width="36" customWidth="1" min="21" max="21"/>
     <col width="14" customWidth="1" min="22" max="22"/>
     <col width="14" customWidth="1" min="23" max="23"/>
     <col width="12" customWidth="1" min="24" max="24"/>
@@ -680,7 +680,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -734,7 +734,7 @@
       </c>
       <c r="AD2" s="2" t="inlineStr">
         <is>
-          <t>1/13</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -843,14 +843,14 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB3" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB3" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
           <t>74.0</t>
@@ -858,7 +858,7 @@
       </c>
       <c r="AD3" s="2" t="inlineStr">
         <is>
-          <t>2/13</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -901,24 +901,24 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>07:41</t>
+          <t>07:45</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>81分钟</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr"/>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -977,12 +977,12 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AD4" s="2" t="inlineStr">
         <is>
-          <t>3/13</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -1015,32 +1015,36 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr"/>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
           <t>05:50</t>
@@ -1048,7 +1052,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -1072,17 +1076,17 @@
       </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
@@ -1092,13 +1096,17 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC5" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC5" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
       <c r="AD5" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -1141,24 +1149,24 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>07:56</t>
+          <t>08:07</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>81分钟</t>
+          <t>92分钟</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr"/>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
@@ -1168,7 +1176,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1207,22 +1215,22 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB6" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB6" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="AD6" s="2" t="inlineStr">
         <is>
-          <t>3/13</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1263,36 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:13</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr"/>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
           <t>06:12</t>
@@ -1288,7 +1300,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1312,33 +1324,37 @@
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC7" s="2" t="inlineStr"/>
+      <c r="AC7" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
       <c r="AD7" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -1371,32 +1387,36 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:27</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>92分钟</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr"/>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
           <t>05:50</t>
@@ -1404,7 +1424,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1428,33 +1448,37 @@
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB8" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC8" s="2" t="inlineStr"/>
+      <c r="AC8" s="2" t="inlineStr">
+        <is>
+          <t>92.0</t>
+        </is>
+      </c>
       <c r="AD8" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -1487,32 +1511,36 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr"/>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
           <t>06:22</t>
@@ -1520,7 +1548,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1544,33 +1572,37 @@
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB9" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC9" s="2" t="inlineStr"/>
+      <c r="AC9" s="2" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
       <c r="AD9" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -1603,32 +1635,36 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:44</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>92分钟</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr"/>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -1636,7 +1672,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1660,33 +1696,37 @@
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC10" s="2" t="inlineStr"/>
+      <c r="AC10" s="2" t="inlineStr">
+        <is>
+          <t>92.0</t>
+        </is>
+      </c>
       <c r="AD10" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -1719,32 +1759,36 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:48</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>93分钟</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr"/>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1752,7 +1796,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1776,33 +1820,37 @@
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB11" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC11" s="2" t="inlineStr"/>
+      <c r="AC11" s="2" t="inlineStr">
+        <is>
+          <t>93.0</t>
+        </is>
+      </c>
       <c r="AD11" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -1868,7 +1916,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1918,7 +1966,7 @@
       <c r="AC12" s="2" t="inlineStr"/>
       <c r="AD12" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -1984,7 +2032,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -2038,7 +2086,7 @@
       </c>
       <c r="AD13" s="2" t="inlineStr">
         <is>
-          <t>1/13</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -2104,7 +2152,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2154,7 +2202,7 @@
       <c r="AC14" s="2" t="inlineStr"/>
       <c r="AD14" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -2220,7 +2268,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2270,7 +2318,7 @@
       <c r="AC15" s="2" t="inlineStr"/>
       <c r="AD15" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -2336,7 +2384,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2385,12 +2433,12 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AD16" s="2" t="inlineStr">
         <is>
-          <t>3/13</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -2403,22 +2451,22 @@
       <c r="B17" s="2" t="inlineStr"/>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>沪A67026D</t>
+          <t>沪A55712D</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
           <t>金杨路金口路</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>08:15</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2456,7 +2504,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2470,7 +2518,7 @@
       <c r="U17" s="2" t="inlineStr"/>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2500,83 +2548,83 @@
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC17" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC17" s="2" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
+      </c>
       <c r="AD17" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr"/>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>沪A09172D</t>
+          <t>沪A67026D</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>05:50</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>131分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr"/>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr"/>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>05:49</t>
+          <t>05:50</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2590,7 +2638,7 @@
       <c r="U18" s="2" t="inlineStr"/>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>05:50</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
@@ -2600,107 +2648,103 @@
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y18" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB18" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB18" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AD18" s="2" t="inlineStr">
         <is>
-          <t>1/20</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr"/>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>沪A62880D</t>
+          <t>沪A67983D</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>05:50</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>08:05</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>135分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr"/>
       <c r="L19" s="2" t="inlineStr"/>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr"/>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>05:49</t>
+          <t>05:50</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2714,7 +2758,7 @@
       <c r="U19" s="2" t="inlineStr"/>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>05:50</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -2724,65 +2768,65 @@
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y19" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB19" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="AD19" s="2" t="inlineStr">
         <is>
-          <t>2/20</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr"/>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>沪A57051D</t>
+          <t>沪A08953A</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2815,12 +2859,12 @@
       <c r="N20" s="2" t="inlineStr"/>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>05:49</t>
+          <t>07:51</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2834,7 +2878,7 @@
       <c r="U20" s="2" t="inlineStr"/>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2870,35 +2914,35 @@
       <c r="AC20" s="2" t="inlineStr"/>
       <c r="AD20" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr"/>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>沪A66883D</t>
+          <t>沪A68870D</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2931,12 +2975,12 @@
       <c r="N21" s="2" t="inlineStr"/>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>05:49</t>
+          <t>06:12</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2950,7 +2994,7 @@
       <c r="U21" s="2" t="inlineStr"/>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
@@ -2975,46 +3019,50 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB21" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB21" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC21" s="2" t="inlineStr"/>
+      <c r="AC21" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
       <c r="AD21" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr"/>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>沪A51682D</t>
+          <t>沪A13735A</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -3047,12 +3095,12 @@
       <c r="N22" s="2" t="inlineStr"/>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>05:49</t>
+          <t>05:50</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -3066,7 +3114,7 @@
       <c r="U22" s="2" t="inlineStr"/>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -3091,46 +3139,50 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB22" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC22" s="2" t="inlineStr"/>
+      <c r="AC22" s="2" t="inlineStr">
+        <is>
+          <t>92.0</t>
+        </is>
+      </c>
       <c r="AD22" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr"/>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>沪A71572D</t>
+          <t>沪A32899D</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3163,12 +3215,12 @@
       <c r="N23" s="2" t="inlineStr"/>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>05:49</t>
+          <t>06:22</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -3182,7 +3234,7 @@
       <c r="U23" s="2" t="inlineStr"/>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3207,46 +3259,50 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC23" s="2" t="inlineStr"/>
+      <c r="AC23" s="2" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
       <c r="AD23" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr"/>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>沪A11062A</t>
+          <t>沪A66513D</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3279,12 +3335,12 @@
       <c r="N24" s="2" t="inlineStr"/>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3298,7 +3354,7 @@
       <c r="U24" s="2" t="inlineStr"/>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
@@ -3323,46 +3379,50 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB24" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC24" s="2" t="inlineStr"/>
+      <c r="AC24" s="2" t="inlineStr">
+        <is>
+          <t>92.0</t>
+        </is>
+      </c>
       <c r="AD24" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr"/>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>沪A37823D</t>
+          <t>沪A67353D</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3395,12 +3455,12 @@
       <c r="N25" s="2" t="inlineStr"/>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3414,7 +3474,7 @@
       <c r="U25" s="2" t="inlineStr"/>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -3439,18 +3499,22 @@
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC25" s="2" t="inlineStr"/>
+      <c r="AC25" s="2" t="inlineStr">
+        <is>
+          <t>93.0</t>
+        </is>
+      </c>
       <c r="AD25" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -3463,60 +3527,64 @@
       <c r="B26" s="2" t="inlineStr"/>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>沪A70597D</t>
+          <t>沪A09172D</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>05:50</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>06:42</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>124分钟</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr"/>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>05:49</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3530,7 +3598,7 @@
       <c r="U26" s="2" t="inlineStr"/>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>05:50</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3540,33 +3608,37 @@
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC26" s="2" t="inlineStr"/>
+      <c r="AC26" s="2" t="inlineStr">
+        <is>
+          <t>124.0</t>
+        </is>
+      </c>
       <c r="AD26" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>1/25</t>
         </is>
       </c>
     </row>
@@ -3579,7 +3651,7 @@
       <c r="B27" s="2" t="inlineStr"/>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>沪A95621D</t>
+          <t>沪A62880D</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -3589,7 +3661,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>05:50</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -3599,40 +3671,44 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:13</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>143分钟</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr"/>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N27" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>05:49</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3646,7 +3722,7 @@
       <c r="U27" s="2" t="inlineStr"/>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>05:50</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
@@ -3656,33 +3732,37 @@
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB27" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC27" s="2" t="inlineStr"/>
+      <c r="AC27" s="2" t="inlineStr">
+        <is>
+          <t>143.0</t>
+        </is>
+      </c>
       <c r="AD27" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>2/25</t>
         </is>
       </c>
     </row>
@@ -3695,7 +3775,7 @@
       <c r="B28" s="2" t="inlineStr"/>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>沪A37267D</t>
+          <t>沪A57051D</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -3705,7 +3785,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>06:56</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -3743,12 +3823,12 @@
       <c r="N28" s="2" t="inlineStr"/>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>05:49</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3762,7 +3842,7 @@
       <c r="U28" s="2" t="inlineStr"/>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>06:56</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -3787,7 +3867,7 @@
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
@@ -3798,7 +3878,7 @@
       <c r="AC28" s="2" t="inlineStr"/>
       <c r="AD28" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -3811,7 +3891,7 @@
       <c r="B29" s="2" t="inlineStr"/>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>沪A73927D</t>
+          <t>沪A66883D</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -3821,7 +3901,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -3831,40 +3911,44 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:38</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>148分钟</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr"/>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>05:49</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3878,7 +3962,7 @@
       <c r="U29" s="2" t="inlineStr"/>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -3888,33 +3972,37 @@
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB29" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB29" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC29" s="2" t="inlineStr"/>
+      <c r="AC29" s="2" t="inlineStr">
+        <is>
+          <t>148.0</t>
+        </is>
+      </c>
       <c r="AD29" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>3/25</t>
         </is>
       </c>
     </row>
@@ -3927,7 +4015,7 @@
       <c r="B30" s="2" t="inlineStr"/>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>沪A55102D</t>
+          <t>沪A51682D</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -3937,7 +4025,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>06:26</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -3975,12 +4063,12 @@
       <c r="N30" s="2" t="inlineStr"/>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>05:49</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3994,7 +4082,7 @@
       <c r="U30" s="2" t="inlineStr"/>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>06:26</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
@@ -4030,7 +4118,7 @@
       <c r="AC30" s="2" t="inlineStr"/>
       <c r="AD30" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -4043,7 +4131,7 @@
       <c r="B31" s="2" t="inlineStr"/>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>沪A36993D</t>
+          <t>沪A71572D</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -4053,7 +4141,7 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -4091,12 +4179,12 @@
       <c r="N31" s="2" t="inlineStr"/>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>05:49</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -4110,7 +4198,7 @@
       <c r="U31" s="2" t="inlineStr"/>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
@@ -4135,7 +4223,7 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
@@ -4146,7 +4234,7 @@
       <c r="AC31" s="2" t="inlineStr"/>
       <c r="AD31" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -4159,7 +4247,7 @@
       <c r="B32" s="2" t="inlineStr"/>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>沪A67057D</t>
+          <t>沪A11062A</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -4169,7 +4257,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>07:26</t>
+          <t>06:36</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -4179,12 +4267,12 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程49%处后消失；随后反向物理轨迹由seq28推进至seq38，推进10站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -4207,12 +4295,12 @@
       <c r="N32" s="2" t="inlineStr"/>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -4220,13 +4308,29 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R32" s="2" t="inlineStr"/>
-      <c r="S32" s="2" t="inlineStr"/>
-      <c r="T32" s="2" t="inlineStr"/>
-      <c r="U32" s="2" t="inlineStr"/>
+      <c r="R32" s="2" t="inlineStr">
+        <is>
+          <t>物理seq32（站名待映射）</t>
+        </is>
+      </c>
+      <c r="S32" s="2" t="inlineStr">
+        <is>
+          <t>07:52</t>
+        </is>
+      </c>
+      <c r="T32" s="2" t="inlineStr">
+        <is>
+          <t>07:56</t>
+        </is>
+      </c>
+      <c r="U32" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq32映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±5分钟；反向位置物理seq28（站名待映射） ETA 0分钟参与校验</t>
+        </is>
+      </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>07:26</t>
+          <t>06:36</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
@@ -4262,7 +4366,7 @@
       <c r="AC32" s="2" t="inlineStr"/>
       <c r="AD32" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -4275,22 +4379,22 @@
       <c r="B33" s="2" t="inlineStr"/>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>沪A72873D</t>
+          <t>沪A37823D</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4323,12 +4427,12 @@
       <c r="N33" s="2" t="inlineStr"/>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4342,7 +4446,7 @@
       <c r="U33" s="2" t="inlineStr"/>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
@@ -4378,7 +4482,7 @@
       <c r="AC33" s="2" t="inlineStr"/>
       <c r="AD33" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -4391,22 +4495,22 @@
       <c r="B34" s="2" t="inlineStr"/>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>沪A67712D</t>
+          <t>沪A70597D</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>07:41</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4439,12 +4543,12 @@
       <c r="N34" s="2" t="inlineStr"/>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4458,7 +4562,7 @@
       <c r="U34" s="2" t="inlineStr"/>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>07:41</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
@@ -4494,7 +4598,7 @@
       <c r="AC34" s="2" t="inlineStr"/>
       <c r="AD34" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -4507,7 +4611,7 @@
       <c r="B35" s="2" t="inlineStr"/>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>沪A90275D</t>
+          <t>沪A95621D</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -4517,7 +4621,7 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
@@ -4555,12 +4659,12 @@
       <c r="N35" s="2" t="inlineStr"/>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4574,7 +4678,7 @@
       <c r="U35" s="2" t="inlineStr"/>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
@@ -4610,7 +4714,7 @@
       <c r="AC35" s="2" t="inlineStr"/>
       <c r="AD35" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -4623,22 +4727,22 @@
       <c r="B36" s="2" t="inlineStr"/>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>沪A02891D</t>
+          <t>沪A37267D</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>06:56</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>07:54</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4671,12 +4775,12 @@
       <c r="N36" s="2" t="inlineStr"/>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4690,7 +4794,7 @@
       <c r="U36" s="2" t="inlineStr"/>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>06:56</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
@@ -4726,7 +4830,7 @@
       <c r="AC36" s="2" t="inlineStr"/>
       <c r="AD36" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -4739,22 +4843,22 @@
       <c r="B37" s="2" t="inlineStr"/>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>沪A62981D</t>
+          <t>沪A73927D</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>07:54</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4787,12 +4891,12 @@
       <c r="N37" s="2" t="inlineStr"/>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4806,7 +4910,7 @@
       <c r="U37" s="2" t="inlineStr"/>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
@@ -4842,35 +4946,35 @@
       <c r="AC37" s="2" t="inlineStr"/>
       <c r="AD37" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr"/>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A55102D</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>05:58</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4903,12 +5007,12 @@
       <c r="N38" s="2" t="inlineStr"/>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>05:48</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4922,7 +5026,7 @@
       <c r="U38" s="2" t="inlineStr"/>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>05:58</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
@@ -4947,7 +5051,7 @@
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
@@ -4958,35 +5062,35 @@
       <c r="AC38" s="2" t="inlineStr"/>
       <c r="AD38" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr"/>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>沪A35616D</t>
+          <t>沪A36993D</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -5019,12 +5123,12 @@
       <c r="N39" s="2" t="inlineStr"/>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>05:48</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -5038,7 +5142,7 @@
       <c r="U39" s="2" t="inlineStr"/>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
@@ -5063,7 +5167,7 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
@@ -5074,35 +5178,35 @@
       <c r="AC39" s="2" t="inlineStr"/>
       <c r="AD39" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr"/>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>沪A57022D</t>
+          <t>沪A67057D</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>07:26</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -5135,12 +5239,12 @@
       <c r="N40" s="2" t="inlineStr"/>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>05:48</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -5154,7 +5258,7 @@
       <c r="U40" s="2" t="inlineStr"/>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>07:26</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
@@ -5190,35 +5294,35 @@
       <c r="AC40" s="2" t="inlineStr"/>
       <c r="AD40" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr"/>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>沪A36809D</t>
+          <t>沪A72873D</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -5251,12 +5355,12 @@
       <c r="N41" s="2" t="inlineStr"/>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5270,7 +5374,7 @@
       <c r="U41" s="2" t="inlineStr"/>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
@@ -5306,35 +5410,35 @@
       <c r="AC41" s="2" t="inlineStr"/>
       <c r="AD41" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr"/>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>沪A61166D</t>
+          <t>沪A67712D</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>07:41</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5367,12 +5471,12 @@
       <c r="N42" s="2" t="inlineStr"/>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5386,7 +5490,7 @@
       <c r="U42" s="2" t="inlineStr"/>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>07:41</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
@@ -5422,35 +5526,35 @@
       <c r="AC42" s="2" t="inlineStr"/>
       <c r="AD42" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr"/>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>沪A35172D</t>
+          <t>沪A90275D</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5483,12 +5587,12 @@
       <c r="N43" s="2" t="inlineStr"/>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5502,7 +5606,7 @@
       <c r="U43" s="2" t="inlineStr"/>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
@@ -5538,35 +5642,35 @@
       <c r="AC43" s="2" t="inlineStr"/>
       <c r="AD43" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr"/>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>沪A66391D</t>
+          <t>沪A02891D</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5599,12 +5703,12 @@
       <c r="N44" s="2" t="inlineStr"/>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5618,7 +5722,7 @@
       <c r="U44" s="2" t="inlineStr"/>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
@@ -5654,35 +5758,35 @@
       <c r="AC44" s="2" t="inlineStr"/>
       <c r="AD44" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr"/>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>沪A35591D</t>
+          <t>沪A62981D</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5715,12 +5819,12 @@
       <c r="N45" s="2" t="inlineStr"/>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5734,7 +5838,7 @@
       <c r="U45" s="2" t="inlineStr"/>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
@@ -5770,35 +5874,35 @@
       <c r="AC45" s="2" t="inlineStr"/>
       <c r="AD45" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr"/>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A68375D</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5831,12 +5935,12 @@
       <c r="N46" s="2" t="inlineStr"/>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5850,7 +5954,7 @@
       <c r="U46" s="2" t="inlineStr"/>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
@@ -5886,35 +5990,35 @@
       <c r="AC46" s="2" t="inlineStr"/>
       <c r="AD46" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr"/>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>沪A51173D</t>
+          <t>沪A68895D</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5947,12 +6051,12 @@
       <c r="N47" s="2" t="inlineStr"/>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>05:49</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5966,7 +6070,7 @@
       <c r="U47" s="2" t="inlineStr"/>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
@@ -6002,35 +6106,35 @@
       <c r="AC47" s="2" t="inlineStr"/>
       <c r="AD47" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr"/>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A65668D</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -6063,12 +6167,12 @@
       <c r="N48" s="2" t="inlineStr"/>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>05:49</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -6082,7 +6186,7 @@
       <c r="U48" s="2" t="inlineStr"/>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
@@ -6118,35 +6222,35 @@
       <c r="AC48" s="2" t="inlineStr"/>
       <c r="AD48" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr"/>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>沪A56123D</t>
+          <t>沪A02316D</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:25</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -6179,12 +6283,12 @@
       <c r="N49" s="2" t="inlineStr"/>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -6198,7 +6302,7 @@
       <c r="U49" s="2" t="inlineStr"/>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:25</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
@@ -6234,35 +6338,35 @@
       <c r="AC49" s="2" t="inlineStr"/>
       <c r="AD49" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr"/>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A62880D</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -6295,12 +6399,12 @@
       <c r="N50" s="2" t="inlineStr"/>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>05:49</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6314,7 +6418,7 @@
       <c r="U50" s="2" t="inlineStr"/>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
@@ -6339,46 +6443,50 @@
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB50" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB50" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC50" s="2" t="inlineStr"/>
+      <c r="AC50" s="2" t="inlineStr">
+        <is>
+          <t>143.0</t>
+        </is>
+      </c>
       <c r="AD50" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>2/25</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr"/>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>沪A55150D</t>
+          <t>沪A09172D</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -6411,12 +6519,12 @@
       <c r="N51" s="2" t="inlineStr"/>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>05:48</t>
+          <t>05:49</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -6430,7 +6538,7 @@
       <c r="U51" s="2" t="inlineStr"/>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="W51" s="2" t="inlineStr">
@@ -6455,46 +6563,50 @@
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB51" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB51" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC51" s="2" t="inlineStr"/>
+      <c r="AC51" s="2" t="inlineStr">
+        <is>
+          <t>124.0</t>
+        </is>
+      </c>
       <c r="AD51" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>1/25</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr"/>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>沪A53629D</t>
+          <t>沪A66883D</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -6527,12 +6639,12 @@
       <c r="N52" s="2" t="inlineStr"/>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>05:49</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6546,7 +6658,7 @@
       <c r="U52" s="2" t="inlineStr"/>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
@@ -6571,46 +6683,50 @@
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB52" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB52" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC52" s="2" t="inlineStr"/>
+      <c r="AC52" s="2" t="inlineStr">
+        <is>
+          <t>148.0</t>
+        </is>
+      </c>
       <c r="AD52" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>3/25</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr"/>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A05218D</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>07:45</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -6643,12 +6759,12 @@
       <c r="N53" s="2" t="inlineStr"/>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>05:48</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6662,7 +6778,7 @@
       <c r="U53" s="2" t="inlineStr"/>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>07:45</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
@@ -6687,7 +6803,7 @@
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
@@ -6698,35 +6814,35 @@
       <c r="AC53" s="2" t="inlineStr"/>
       <c r="AD53" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr"/>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>沪A35616D</t>
+          <t>沪A57051D</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>07:57</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -6759,12 +6875,12 @@
       <c r="N54" s="2" t="inlineStr"/>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>05:48</t>
+          <t>05:49</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6778,7 +6894,7 @@
       <c r="U54" s="2" t="inlineStr"/>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>07:57</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
@@ -6814,7 +6930,3303 @@
       <c r="AC54" s="2" t="inlineStr"/>
       <c r="AD54" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/25</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr"/>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>沪A71572D</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K55" s="2" t="inlineStr"/>
+      <c r="L55" s="2" t="inlineStr"/>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N55" s="2" t="inlineStr"/>
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t>05:49</t>
+        </is>
+      </c>
+      <c r="P55" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q55" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R55" s="2" t="inlineStr"/>
+      <c r="S55" s="2" t="inlineStr"/>
+      <c r="T55" s="2" t="inlineStr"/>
+      <c r="U55" s="2" t="inlineStr"/>
+      <c r="V55" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="W55" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X55" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z55" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA55" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB55" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC55" s="2" t="inlineStr"/>
+      <c r="AD55" s="2" t="inlineStr">
+        <is>
+          <t>—/25</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr"/>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>05:58</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K56" s="2" t="inlineStr"/>
+      <c r="L56" s="2" t="inlineStr"/>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N56" s="2" t="inlineStr"/>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>05:48</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q56" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R56" s="2" t="inlineStr"/>
+      <c r="S56" s="2" t="inlineStr"/>
+      <c r="T56" s="2" t="inlineStr"/>
+      <c r="U56" s="2" t="inlineStr"/>
+      <c r="V56" s="2" t="inlineStr">
+        <is>
+          <t>05:58</t>
+        </is>
+      </c>
+      <c r="W56" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X56" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z56" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA56" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB56" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC56" s="2" t="inlineStr"/>
+      <c r="AD56" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr"/>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K57" s="2" t="inlineStr"/>
+      <c r="L57" s="2" t="inlineStr"/>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N57" s="2" t="inlineStr"/>
+      <c r="O57" s="2" t="inlineStr">
+        <is>
+          <t>05:48</t>
+        </is>
+      </c>
+      <c r="P57" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q57" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R57" s="2" t="inlineStr"/>
+      <c r="S57" s="2" t="inlineStr"/>
+      <c r="T57" s="2" t="inlineStr"/>
+      <c r="U57" s="2" t="inlineStr"/>
+      <c r="V57" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="W57" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X57" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z57" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA57" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB57" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC57" s="2" t="inlineStr"/>
+      <c r="AD57" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr"/>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>06:25</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K58" s="2" t="inlineStr"/>
+      <c r="L58" s="2" t="inlineStr"/>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N58" s="2" t="inlineStr"/>
+      <c r="O58" s="2" t="inlineStr">
+        <is>
+          <t>05:48</t>
+        </is>
+      </c>
+      <c r="P58" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q58" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R58" s="2" t="inlineStr"/>
+      <c r="S58" s="2" t="inlineStr"/>
+      <c r="T58" s="2" t="inlineStr"/>
+      <c r="U58" s="2" t="inlineStr"/>
+      <c r="V58" s="2" t="inlineStr">
+        <is>
+          <t>06:25</t>
+        </is>
+      </c>
+      <c r="W58" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X58" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z58" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB58" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC58" s="2" t="inlineStr"/>
+      <c r="AD58" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr"/>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>08:12</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr">
+        <is>
+          <t>92分钟</t>
+        </is>
+      </c>
+      <c r="K59" s="2" t="inlineStr"/>
+      <c r="L59" s="2" t="inlineStr"/>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N59" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O59" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P59" s="2" t="inlineStr">
+        <is>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="Q59" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R59" s="2" t="inlineStr"/>
+      <c r="S59" s="2" t="inlineStr"/>
+      <c r="T59" s="2" t="inlineStr"/>
+      <c r="U59" s="2" t="inlineStr"/>
+      <c r="V59" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="W59" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X59" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y59" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z59" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA59" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB59" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC59" s="2" t="inlineStr">
+        <is>
+          <t>92.0</t>
+        </is>
+      </c>
+      <c r="AD59" s="2" t="inlineStr">
+        <is>
+          <t>4/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr"/>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>08:11</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>91分钟</t>
+        </is>
+      </c>
+      <c r="K60" s="2" t="inlineStr"/>
+      <c r="L60" s="2" t="inlineStr"/>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N60" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P60" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q60" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R60" s="2" t="inlineStr"/>
+      <c r="S60" s="2" t="inlineStr"/>
+      <c r="T60" s="2" t="inlineStr"/>
+      <c r="U60" s="2" t="inlineStr"/>
+      <c r="V60" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="W60" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X60" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y60" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z60" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA60" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB60" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC60" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
+      <c r="AD60" s="2" t="inlineStr">
+        <is>
+          <t>3/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr"/>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K61" s="2" t="inlineStr"/>
+      <c r="L61" s="2" t="inlineStr"/>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N61" s="2" t="inlineStr"/>
+      <c r="O61" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="P61" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q61" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R61" s="2" t="inlineStr"/>
+      <c r="S61" s="2" t="inlineStr"/>
+      <c r="T61" s="2" t="inlineStr"/>
+      <c r="U61" s="2" t="inlineStr"/>
+      <c r="V61" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="W61" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X61" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z61" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA61" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB61" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC61" s="2" t="inlineStr"/>
+      <c r="AD61" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr"/>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>08:17</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>87分钟</t>
+        </is>
+      </c>
+      <c r="K62" s="2" t="inlineStr"/>
+      <c r="L62" s="2" t="inlineStr"/>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N62" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O62" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P62" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q62" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R62" s="2" t="inlineStr"/>
+      <c r="S62" s="2" t="inlineStr"/>
+      <c r="T62" s="2" t="inlineStr"/>
+      <c r="U62" s="2" t="inlineStr"/>
+      <c r="V62" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="W62" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X62" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y62" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z62" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA62" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB62" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC62" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
+      <c r="AD62" s="2" t="inlineStr">
+        <is>
+          <t>2/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr"/>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K63" s="2" t="inlineStr"/>
+      <c r="L63" s="2" t="inlineStr"/>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N63" s="2" t="inlineStr"/>
+      <c r="O63" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P63" s="2" t="inlineStr">
+        <is>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="Q63" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R63" s="2" t="inlineStr"/>
+      <c r="S63" s="2" t="inlineStr"/>
+      <c r="T63" s="2" t="inlineStr"/>
+      <c r="U63" s="2" t="inlineStr"/>
+      <c r="V63" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="W63" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X63" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z63" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA63" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB63" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC63" s="2" t="inlineStr"/>
+      <c r="AD63" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr"/>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>08:25</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>85分钟</t>
+        </is>
+      </c>
+      <c r="K64" s="2" t="inlineStr"/>
+      <c r="L64" s="2" t="inlineStr"/>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N64" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O64" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P64" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q64" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R64" s="2" t="inlineStr"/>
+      <c r="S64" s="2" t="inlineStr"/>
+      <c r="T64" s="2" t="inlineStr"/>
+      <c r="U64" s="2" t="inlineStr"/>
+      <c r="V64" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="W64" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X64" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y64" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z64" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA64" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB64" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC64" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
+      <c r="AD64" s="2" t="inlineStr">
+        <is>
+          <t>1/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr"/>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K65" s="2" t="inlineStr"/>
+      <c r="L65" s="2" t="inlineStr"/>
+      <c r="M65" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N65" s="2" t="inlineStr"/>
+      <c r="O65" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="P65" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q65" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R65" s="2" t="inlineStr"/>
+      <c r="S65" s="2" t="inlineStr"/>
+      <c r="T65" s="2" t="inlineStr"/>
+      <c r="U65" s="2" t="inlineStr"/>
+      <c r="V65" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="W65" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X65" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z65" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA65" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB65" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC65" s="2" t="inlineStr"/>
+      <c r="AD65" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr"/>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K66" s="2" t="inlineStr"/>
+      <c r="L66" s="2" t="inlineStr"/>
+      <c r="M66" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N66" s="2" t="inlineStr"/>
+      <c r="O66" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="P66" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q66" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R66" s="2" t="inlineStr"/>
+      <c r="S66" s="2" t="inlineStr"/>
+      <c r="T66" s="2" t="inlineStr"/>
+      <c r="U66" s="2" t="inlineStr"/>
+      <c r="V66" s="2" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="W66" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X66" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z66" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA66" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB66" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC66" s="2" t="inlineStr"/>
+      <c r="AD66" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr"/>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K67" s="2" t="inlineStr"/>
+      <c r="L67" s="2" t="inlineStr"/>
+      <c r="M67" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N67" s="2" t="inlineStr"/>
+      <c r="O67" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="P67" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q67" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R67" s="2" t="inlineStr"/>
+      <c r="S67" s="2" t="inlineStr"/>
+      <c r="T67" s="2" t="inlineStr"/>
+      <c r="U67" s="2" t="inlineStr"/>
+      <c r="V67" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="W67" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X67" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z67" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA67" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB67" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC67" s="2" t="inlineStr"/>
+      <c r="AD67" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr"/>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K68" s="2" t="inlineStr"/>
+      <c r="L68" s="2" t="inlineStr"/>
+      <c r="M68" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N68" s="2" t="inlineStr"/>
+      <c r="O68" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="P68" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q68" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R68" s="2" t="inlineStr"/>
+      <c r="S68" s="2" t="inlineStr"/>
+      <c r="T68" s="2" t="inlineStr"/>
+      <c r="U68" s="2" t="inlineStr"/>
+      <c r="V68" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="W68" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X68" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z68" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA68" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB68" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC68" s="2" t="inlineStr"/>
+      <c r="AD68" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr"/>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K69" s="2" t="inlineStr"/>
+      <c r="L69" s="2" t="inlineStr"/>
+      <c r="M69" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N69" s="2" t="inlineStr"/>
+      <c r="O69" s="2" t="inlineStr">
+        <is>
+          <t>05:48</t>
+        </is>
+      </c>
+      <c r="P69" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q69" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R69" s="2" t="inlineStr"/>
+      <c r="S69" s="2" t="inlineStr"/>
+      <c r="T69" s="2" t="inlineStr"/>
+      <c r="U69" s="2" t="inlineStr"/>
+      <c r="V69" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="W69" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X69" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z69" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA69" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB69" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC69" s="2" t="inlineStr"/>
+      <c r="AD69" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr"/>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>沪A53629D</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K70" s="2" t="inlineStr"/>
+      <c r="L70" s="2" t="inlineStr"/>
+      <c r="M70" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N70" s="2" t="inlineStr"/>
+      <c r="O70" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="P70" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q70" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R70" s="2" t="inlineStr"/>
+      <c r="S70" s="2" t="inlineStr"/>
+      <c r="T70" s="2" t="inlineStr"/>
+      <c r="U70" s="2" t="inlineStr"/>
+      <c r="V70" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="W70" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X70" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z70" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA70" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB70" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC70" s="2" t="inlineStr"/>
+      <c r="AD70" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr"/>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>07:45</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K71" s="2" t="inlineStr"/>
+      <c r="L71" s="2" t="inlineStr"/>
+      <c r="M71" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N71" s="2" t="inlineStr"/>
+      <c r="O71" s="2" t="inlineStr">
+        <is>
+          <t>05:48</t>
+        </is>
+      </c>
+      <c r="P71" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q71" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R71" s="2" t="inlineStr"/>
+      <c r="S71" s="2" t="inlineStr"/>
+      <c r="T71" s="2" t="inlineStr"/>
+      <c r="U71" s="2" t="inlineStr"/>
+      <c r="V71" s="2" t="inlineStr">
+        <is>
+          <t>07:45</t>
+        </is>
+      </c>
+      <c r="W71" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X71" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z71" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA71" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB71" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC71" s="2" t="inlineStr"/>
+      <c r="AD71" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr"/>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K72" s="2" t="inlineStr"/>
+      <c r="L72" s="2" t="inlineStr"/>
+      <c r="M72" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N72" s="2" t="inlineStr"/>
+      <c r="O72" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P72" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q72" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R72" s="2" t="inlineStr"/>
+      <c r="S72" s="2" t="inlineStr"/>
+      <c r="T72" s="2" t="inlineStr"/>
+      <c r="U72" s="2" t="inlineStr"/>
+      <c r="V72" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="W72" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X72" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z72" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA72" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB72" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC72" s="2" t="inlineStr"/>
+      <c r="AD72" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr"/>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>07:57</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K73" s="2" t="inlineStr"/>
+      <c r="L73" s="2" t="inlineStr"/>
+      <c r="M73" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N73" s="2" t="inlineStr"/>
+      <c r="O73" s="2" t="inlineStr">
+        <is>
+          <t>05:48</t>
+        </is>
+      </c>
+      <c r="P73" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q73" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R73" s="2" t="inlineStr"/>
+      <c r="S73" s="2" t="inlineStr"/>
+      <c r="T73" s="2" t="inlineStr"/>
+      <c r="U73" s="2" t="inlineStr"/>
+      <c r="V73" s="2" t="inlineStr">
+        <is>
+          <t>07:57</t>
+        </is>
+      </c>
+      <c r="W73" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X73" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z73" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA73" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB73" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC73" s="2" t="inlineStr"/>
+      <c r="AD73" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr"/>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>沪A57902D</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K74" s="2" t="inlineStr"/>
+      <c r="L74" s="2" t="inlineStr"/>
+      <c r="M74" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N74" s="2" t="inlineStr"/>
+      <c r="O74" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="P74" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q74" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R74" s="2" t="inlineStr"/>
+      <c r="S74" s="2" t="inlineStr"/>
+      <c r="T74" s="2" t="inlineStr"/>
+      <c r="U74" s="2" t="inlineStr"/>
+      <c r="V74" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="W74" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X74" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z74" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA74" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB74" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC74" s="2" t="inlineStr"/>
+      <c r="AD74" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr"/>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>08:09</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K75" s="2" t="inlineStr"/>
+      <c r="L75" s="2" t="inlineStr"/>
+      <c r="M75" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N75" s="2" t="inlineStr"/>
+      <c r="O75" s="2" t="inlineStr">
+        <is>
+          <t>05:48</t>
+        </is>
+      </c>
+      <c r="P75" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q75" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R75" s="2" t="inlineStr"/>
+      <c r="S75" s="2" t="inlineStr"/>
+      <c r="T75" s="2" t="inlineStr"/>
+      <c r="U75" s="2" t="inlineStr"/>
+      <c r="V75" s="2" t="inlineStr">
+        <is>
+          <t>08:09</t>
+        </is>
+      </c>
+      <c r="W75" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X75" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z75" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA75" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB75" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC75" s="2" t="inlineStr"/>
+      <c r="AD75" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr"/>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K76" s="2" t="inlineStr"/>
+      <c r="L76" s="2" t="inlineStr"/>
+      <c r="M76" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N76" s="2" t="inlineStr"/>
+      <c r="O76" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P76" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q76" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R76" s="2" t="inlineStr"/>
+      <c r="S76" s="2" t="inlineStr"/>
+      <c r="T76" s="2" t="inlineStr"/>
+      <c r="U76" s="2" t="inlineStr"/>
+      <c r="V76" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="W76" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X76" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z76" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA76" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB76" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC76" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
+      <c r="AD76" s="2" t="inlineStr">
+        <is>
+          <t>3/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr"/>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K77" s="2" t="inlineStr"/>
+      <c r="L77" s="2" t="inlineStr"/>
+      <c r="M77" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N77" s="2" t="inlineStr"/>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P77" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q77" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R77" s="2" t="inlineStr"/>
+      <c r="S77" s="2" t="inlineStr"/>
+      <c r="T77" s="2" t="inlineStr"/>
+      <c r="U77" s="2" t="inlineStr"/>
+      <c r="V77" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="W77" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X77" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z77" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA77" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB77" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC77" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
+      <c r="AD77" s="2" t="inlineStr">
+        <is>
+          <t>2/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr"/>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>08:33</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K78" s="2" t="inlineStr"/>
+      <c r="L78" s="2" t="inlineStr"/>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N78" s="2" t="inlineStr"/>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P78" s="2" t="inlineStr">
+        <is>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="Q78" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R78" s="2" t="inlineStr"/>
+      <c r="S78" s="2" t="inlineStr"/>
+      <c r="T78" s="2" t="inlineStr"/>
+      <c r="U78" s="2" t="inlineStr"/>
+      <c r="V78" s="2" t="inlineStr">
+        <is>
+          <t>08:33</t>
+        </is>
+      </c>
+      <c r="W78" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X78" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z78" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA78" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB78" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC78" s="2" t="inlineStr">
+        <is>
+          <t>92.0</t>
+        </is>
+      </c>
+      <c r="AD78" s="2" t="inlineStr">
+        <is>
+          <t>4/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr"/>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>沪A36930D</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>08:33</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K79" s="2" t="inlineStr"/>
+      <c r="L79" s="2" t="inlineStr"/>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N79" s="2" t="inlineStr"/>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>07:40</t>
+        </is>
+      </c>
+      <c r="P79" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q79" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R79" s="2" t="inlineStr"/>
+      <c r="S79" s="2" t="inlineStr"/>
+      <c r="T79" s="2" t="inlineStr"/>
+      <c r="U79" s="2" t="inlineStr"/>
+      <c r="V79" s="2" t="inlineStr">
+        <is>
+          <t>08:33</t>
+        </is>
+      </c>
+      <c r="W79" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X79" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z79" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA79" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB79" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC79" s="2" t="inlineStr"/>
+      <c r="AD79" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr"/>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K80" s="2" t="inlineStr"/>
+      <c r="L80" s="2" t="inlineStr"/>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N80" s="2" t="inlineStr"/>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="P80" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q80" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R80" s="2" t="inlineStr"/>
+      <c r="S80" s="2" t="inlineStr"/>
+      <c r="T80" s="2" t="inlineStr"/>
+      <c r="U80" s="2" t="inlineStr"/>
+      <c r="V80" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="W80" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X80" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z80" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA80" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB80" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC80" s="2" t="inlineStr"/>
+      <c r="AD80" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr"/>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K81" s="2" t="inlineStr"/>
+      <c r="L81" s="2" t="inlineStr"/>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N81" s="2" t="inlineStr"/>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P81" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q81" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R81" s="2" t="inlineStr"/>
+      <c r="S81" s="2" t="inlineStr"/>
+      <c r="T81" s="2" t="inlineStr"/>
+      <c r="U81" s="2" t="inlineStr"/>
+      <c r="V81" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="W81" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X81" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z81" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA81" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB81" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC81" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
+      <c r="AD81" s="2" t="inlineStr">
+        <is>
+          <t>1/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr"/>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K82" s="2" t="inlineStr"/>
+      <c r="L82" s="2" t="inlineStr"/>
+      <c r="M82" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N82" s="2" t="inlineStr"/>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="P82" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q82" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R82" s="2" t="inlineStr"/>
+      <c r="S82" s="2" t="inlineStr"/>
+      <c r="T82" s="2" t="inlineStr"/>
+      <c r="U82" s="2" t="inlineStr"/>
+      <c r="V82" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="W82" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X82" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z82" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA82" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB82" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC82" s="2" t="inlineStr"/>
+      <c r="AD82" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-13-operations.xlsx
+++ b/data/export/2026-10-13-operations.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD82"/>
+  <dimension ref="A1:AD104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -680,7 +680,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -719,22 +719,22 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB2" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>83.5</t>
         </is>
       </c>
       <c r="AD2" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -848,12 +848,12 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AD3" s="2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -967,22 +967,22 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB4" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>81.5</t>
         </is>
       </c>
       <c r="AD4" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -1052,7 +1052,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -1091,22 +1091,22 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB5" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB5" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>89.5</t>
         </is>
       </c>
       <c r="AD5" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -1176,7 +1176,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1230,7 +1230,7 @@
       </c>
       <c r="AD6" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1354,7 +1354,7 @@
       </c>
       <c r="AD7" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1478,7 +1478,7 @@
       </c>
       <c r="AD8" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -1548,7 +1548,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1602,7 +1602,7 @@
       </c>
       <c r="AD9" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -1645,24 +1645,24 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>08:44</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>92分钟</t>
+          <t>91分钟</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr"/>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
@@ -1672,7 +1672,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AD10" s="2" t="inlineStr">
@@ -1769,12 +1769,12 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>08:48</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>93分钟</t>
+          <t>94分钟</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr"/>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1845,7 +1845,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>94.0</t>
         </is>
       </c>
       <c r="AD11" s="2" t="inlineStr">
@@ -1916,7 +1916,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
@@ -1999,32 +1999,36 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>95分钟</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr"/>
       <c r="L13" s="2" t="inlineStr"/>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
           <t>05:50</t>
@@ -2032,7 +2036,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -2056,37 +2060,37 @@
       </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB13" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>83.5</t>
         </is>
       </c>
       <c r="AD13" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -2119,32 +2123,36 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>98分钟</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr"/>
       <c r="L14" s="2" t="inlineStr"/>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
           <t>07:02</t>
@@ -2152,7 +2160,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2176,33 +2184,37 @@
       </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB14" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC14" s="2" t="inlineStr"/>
+      <c r="AC14" s="2" t="inlineStr">
+        <is>
+          <t>98.0</t>
+        </is>
+      </c>
       <c r="AD14" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -2235,32 +2247,36 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>96分钟</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr"/>
       <c r="L15" s="2" t="inlineStr"/>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
           <t>07:22</t>
@@ -2268,7 +2284,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2292,33 +2308,37 @@
       </c>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB15" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB15" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC15" s="2" t="inlineStr"/>
+      <c r="AC15" s="2" t="inlineStr">
+        <is>
+          <t>96.0</t>
+        </is>
+      </c>
       <c r="AD15" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -2351,32 +2371,36 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr"/>
       <c r="L16" s="2" t="inlineStr"/>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
           <t>05:50</t>
@@ -2384,7 +2408,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2408,37 +2432,37 @@
       </c>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB16" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>81.5</t>
         </is>
       </c>
       <c r="AD16" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -2471,32 +2495,36 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>90分钟</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr"/>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
           <t>05:50</t>
@@ -2504,7 +2532,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2528,17 +2556,17 @@
       </c>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
@@ -2548,12 +2576,12 @@
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AD17" s="2" t="inlineStr">
@@ -2591,32 +2619,36 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>94分钟</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr"/>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
           <t>05:50</t>
@@ -2624,7 +2656,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2648,37 +2680,37 @@
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB18" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB18" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>89.5</t>
         </is>
       </c>
       <c r="AD18" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -2744,7 +2776,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2798,7 +2830,7 @@
       </c>
       <c r="AD19" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -2864,7 +2896,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2980,7 +3012,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -3034,7 +3066,7 @@
       </c>
       <c r="AD21" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3132,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -3154,7 +3186,7 @@
       </c>
       <c r="AD22" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -3220,7 +3252,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -3274,7 +3306,7 @@
       </c>
       <c r="AD23" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -3340,7 +3372,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3389,7 +3421,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AD24" s="2" t="inlineStr">
@@ -3460,7 +3492,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3509,7 +3541,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>94.0</t>
         </is>
       </c>
       <c r="AD25" s="2" t="inlineStr">
@@ -3521,70 +3553,66 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr"/>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>沪A09172D</t>
+          <t>沪A31073D</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>05:50</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>124分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr"/>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr"/>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>05:49</t>
+          <t>05:50</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3598,7 +3626,7 @@
       <c r="U26" s="2" t="inlineStr"/>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>05:50</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3608,17 +3636,17 @@
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
@@ -3628,87 +3656,79 @@
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC26" s="2" t="inlineStr">
-        <is>
-          <t>124.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC26" s="2" t="inlineStr"/>
       <c r="AD26" s="2" t="inlineStr">
         <is>
-          <t>1/25</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr"/>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>沪A62880D</t>
+          <t>沪A32298D</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>05:50</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>08:13</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>143分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr"/>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N27" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr"/>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>05:49</t>
+          <t>05:50</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3722,7 +3742,7 @@
       <c r="U27" s="2" t="inlineStr"/>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>05:50</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
@@ -3732,65 +3752,65 @@
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB27" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>83.5</t>
         </is>
       </c>
       <c r="AD27" s="2" t="inlineStr">
         <is>
-          <t>2/25</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr"/>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>沪A57051D</t>
+          <t>沪A35717D</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3823,12 +3843,12 @@
       <c r="N28" s="2" t="inlineStr"/>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>05:49</t>
+          <t>07:02</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3842,7 +3862,7 @@
       <c r="U28" s="2" t="inlineStr"/>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -3872,83 +3892,83 @@
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC28" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC28" s="2" t="inlineStr">
+        <is>
+          <t>98.0</t>
+        </is>
+      </c>
       <c r="AD28" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr"/>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>沪A66883D</t>
+          <t>沪A02126A</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>08:38</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>148分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr"/>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr"/>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>05:49</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3962,7 +3982,7 @@
       <c r="U29" s="2" t="inlineStr"/>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -3972,17 +3992,17 @@
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y29" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
@@ -3997,40 +4017,40 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>148.0</t>
+          <t>96.0</t>
         </is>
       </c>
       <c r="AD29" s="2" t="inlineStr">
         <is>
-          <t>3/25</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr"/>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>沪A51682D</t>
+          <t>沪A68397D</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -4063,12 +4083,12 @@
       <c r="N30" s="2" t="inlineStr"/>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>05:49</t>
+          <t>05:50</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -4082,7 +4102,7 @@
       <c r="U30" s="2" t="inlineStr"/>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
@@ -4107,46 +4127,50 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC30" s="2" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC30" s="2" t="inlineStr">
+        <is>
+          <t>81.5</t>
+        </is>
+      </c>
       <c r="AD30" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr"/>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>沪A71572D</t>
+          <t>沪A67026D</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -4179,12 +4203,12 @@
       <c r="N31" s="2" t="inlineStr"/>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>05:49</t>
+          <t>05:50</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -4198,7 +4222,7 @@
       <c r="U31" s="2" t="inlineStr"/>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
@@ -4223,18 +4247,22 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB31" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC31" s="2" t="inlineStr"/>
+      <c r="AC31" s="2" t="inlineStr">
+        <is>
+          <t>89.5</t>
+        </is>
+      </c>
       <c r="AD31" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -4247,7 +4275,7 @@
       <c r="B32" s="2" t="inlineStr"/>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>沪A11062A</t>
+          <t>沪A09172D</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -4257,7 +4285,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>05:50</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -4267,40 +4295,44 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>疑似区间车</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程49%处后消失；随后反向物理轨迹由seq28推进至seq38，推进10站，达到≥2站确认条件</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>124分钟</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr"/>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N32" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>05:49</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -4308,29 +4340,13 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R32" s="2" t="inlineStr">
-        <is>
-          <t>物理seq32（站名待映射）</t>
-        </is>
-      </c>
-      <c r="S32" s="2" t="inlineStr">
-        <is>
-          <t>07:52</t>
-        </is>
-      </c>
-      <c r="T32" s="2" t="inlineStr">
-        <is>
-          <t>07:56</t>
-        </is>
-      </c>
-      <c r="U32" s="2" t="inlineStr">
-        <is>
-          <t>折返点按重建物理位置seq32映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±5分钟；反向位置物理seq28（站名待映射） ETA 0分钟参与校验</t>
-        </is>
-      </c>
+      <c r="R32" s="2" t="inlineStr"/>
+      <c r="S32" s="2" t="inlineStr"/>
+      <c r="T32" s="2" t="inlineStr"/>
+      <c r="U32" s="2" t="inlineStr"/>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>05:50</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
@@ -4340,33 +4356,37 @@
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB32" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB32" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC32" s="2" t="inlineStr"/>
+      <c r="AC32" s="2" t="inlineStr">
+        <is>
+          <t>124.0</t>
+        </is>
+      </c>
       <c r="AD32" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>1/25</t>
         </is>
       </c>
     </row>
@@ -4379,60 +4399,64 @@
       <c r="B33" s="2" t="inlineStr"/>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>沪A37823D</t>
+          <t>沪A62880D</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>05:50</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>06:41</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:13</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>143分钟</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="inlineStr"/>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N33" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>05:49</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4446,7 +4470,7 @@
       <c r="U33" s="2" t="inlineStr"/>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>05:50</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
@@ -4456,33 +4480,37 @@
       </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB33" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB33" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC33" s="2" t="inlineStr"/>
+      <c r="AC33" s="2" t="inlineStr">
+        <is>
+          <t>143.0</t>
+        </is>
+      </c>
       <c r="AD33" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>2/25</t>
         </is>
       </c>
     </row>
@@ -4495,22 +4523,22 @@
       <c r="B34" s="2" t="inlineStr"/>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>沪A70597D</t>
+          <t>沪A57051D</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>06:42</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4543,12 +4571,12 @@
       <c r="N34" s="2" t="inlineStr"/>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>05:49</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4562,7 +4590,7 @@
       <c r="U34" s="2" t="inlineStr"/>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
@@ -4587,7 +4615,7 @@
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
@@ -4611,7 +4639,7 @@
       <c r="B35" s="2" t="inlineStr"/>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>沪A95621D</t>
+          <t>沪A66883D</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -4621,7 +4649,7 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
@@ -4631,40 +4659,44 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:36</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>146分钟</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr"/>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N35" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>05:49</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4678,7 +4710,7 @@
       <c r="U35" s="2" t="inlineStr"/>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
@@ -4688,33 +4720,37 @@
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB35" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB35" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC35" s="2" t="inlineStr"/>
+      <c r="AC35" s="2" t="inlineStr">
+        <is>
+          <t>146.0</t>
+        </is>
+      </c>
       <c r="AD35" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>3/25</t>
         </is>
       </c>
     </row>
@@ -4727,7 +4763,7 @@
       <c r="B36" s="2" t="inlineStr"/>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>沪A37267D</t>
+          <t>沪A51682D</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -4737,7 +4773,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>06:56</t>
+          <t>06:26</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -4775,12 +4811,12 @@
       <c r="N36" s="2" t="inlineStr"/>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>05:49</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4794,7 +4830,7 @@
       <c r="U36" s="2" t="inlineStr"/>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>06:56</t>
+          <t>06:26</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
@@ -4819,7 +4855,7 @@
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
@@ -4843,7 +4879,7 @@
       <c r="B37" s="2" t="inlineStr"/>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>沪A73927D</t>
+          <t>沪A71572D</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -4853,7 +4889,7 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
@@ -4863,40 +4899,44 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:04</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>153分钟</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="2" t="inlineStr"/>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N37" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>05:49</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4910,7 +4950,7 @@
       <c r="U37" s="2" t="inlineStr"/>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
@@ -4920,33 +4960,37 @@
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB37" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB37" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC37" s="2" t="inlineStr"/>
+      <c r="AC37" s="2" t="inlineStr">
+        <is>
+          <t>153.0</t>
+        </is>
+      </c>
       <c r="AD37" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>5/25</t>
         </is>
       </c>
     </row>
@@ -4959,7 +5003,7 @@
       <c r="B38" s="2" t="inlineStr"/>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>沪A55102D</t>
+          <t>沪A11062A</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -4969,7 +5013,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>06:36</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -4979,12 +5023,12 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程49%处后消失；随后反向物理轨迹由seq28推进至seq64，推进36站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -5007,12 +5051,12 @@
       <c r="N38" s="2" t="inlineStr"/>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -5020,13 +5064,29 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R38" s="2" t="inlineStr"/>
-      <c r="S38" s="2" t="inlineStr"/>
-      <c r="T38" s="2" t="inlineStr"/>
-      <c r="U38" s="2" t="inlineStr"/>
+      <c r="R38" s="2" t="inlineStr">
+        <is>
+          <t>物理seq32（站名待映射）</t>
+        </is>
+      </c>
+      <c r="S38" s="2" t="inlineStr">
+        <is>
+          <t>07:52</t>
+        </is>
+      </c>
+      <c r="T38" s="2" t="inlineStr">
+        <is>
+          <t>07:56</t>
+        </is>
+      </c>
+      <c r="U38" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq32映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±5分钟；反向位置物理seq28（站名待映射） ETA 0分钟参与校验</t>
+        </is>
+      </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>06:36</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
@@ -5051,7 +5111,7 @@
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
@@ -5075,60 +5135,64 @@
       <c r="B39" s="2" t="inlineStr"/>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>沪A36993D</t>
+          <t>沪A37823D</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
-          <t>07:18</t>
-        </is>
-      </c>
-      <c r="F39" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>160分钟</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr"/>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N39" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -5142,7 +5206,7 @@
       <c r="U39" s="2" t="inlineStr"/>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
@@ -5152,33 +5216,37 @@
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB39" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB39" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC39" s="2" t="inlineStr"/>
+      <c r="AC39" s="2" t="inlineStr">
+        <is>
+          <t>160.0</t>
+        </is>
+      </c>
       <c r="AD39" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>6/25</t>
         </is>
       </c>
     </row>
@@ -5191,60 +5259,64 @@
       <c r="B40" s="2" t="inlineStr"/>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>沪A67057D</t>
+          <t>沪A70597D</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>07:26</t>
-        </is>
-      </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>161分钟</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr"/>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N40" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -5258,7 +5330,7 @@
       <c r="U40" s="2" t="inlineStr"/>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>07:26</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
@@ -5268,33 +5340,37 @@
       </c>
       <c r="X40" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB40" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB40" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC40" s="2" t="inlineStr"/>
+      <c r="AC40" s="2" t="inlineStr">
+        <is>
+          <t>161.0</t>
+        </is>
+      </c>
       <c r="AD40" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>7/25</t>
         </is>
       </c>
     </row>
@@ -5307,7 +5383,7 @@
       <c r="B41" s="2" t="inlineStr"/>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>沪A72873D</t>
+          <t>沪A95621D</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -5317,7 +5393,7 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
@@ -5355,12 +5431,12 @@
       <c r="N41" s="2" t="inlineStr"/>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5374,7 +5450,7 @@
       <c r="U41" s="2" t="inlineStr"/>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
@@ -5399,7 +5475,7 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
@@ -5423,7 +5499,7 @@
       <c r="B42" s="2" t="inlineStr"/>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>沪A67712D</t>
+          <t>沪A37267D</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -5433,7 +5509,7 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>07:41</t>
+          <t>06:56</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -5443,40 +5519,44 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>149分钟</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="2" t="inlineStr"/>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N42" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5490,7 +5570,7 @@
       <c r="U42" s="2" t="inlineStr"/>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>07:41</t>
+          <t>06:56</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
@@ -5500,33 +5580,37 @@
       </c>
       <c r="X42" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB42" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB42" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC42" s="2" t="inlineStr"/>
+      <c r="AC42" s="2" t="inlineStr">
+        <is>
+          <t>149.0</t>
+        </is>
+      </c>
       <c r="AD42" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>4/25</t>
         </is>
       </c>
     </row>
@@ -5539,7 +5623,7 @@
       <c r="B43" s="2" t="inlineStr"/>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>沪A90275D</t>
+          <t>沪A73927D</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -5549,7 +5633,7 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
@@ -5587,12 +5671,12 @@
       <c r="N43" s="2" t="inlineStr"/>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5606,7 +5690,7 @@
       <c r="U43" s="2" t="inlineStr"/>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
@@ -5655,22 +5739,22 @@
       <c r="B44" s="2" t="inlineStr"/>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>沪A02891D</t>
+          <t>沪A55102D</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t>07:54</t>
-        </is>
-      </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5703,12 +5787,12 @@
       <c r="N44" s="2" t="inlineStr"/>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5722,7 +5806,7 @@
       <c r="U44" s="2" t="inlineStr"/>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
@@ -5747,7 +5831,7 @@
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
@@ -5771,22 +5855,22 @@
       <c r="B45" s="2" t="inlineStr"/>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>沪A62981D</t>
+          <t>沪A36993D</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E45" s="2" t="inlineStr">
-        <is>
-          <t>07:54</t>
-        </is>
-      </c>
-      <c r="F45" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5819,12 +5903,12 @@
       <c r="N45" s="2" t="inlineStr"/>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5838,7 +5922,7 @@
       <c r="U45" s="2" t="inlineStr"/>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
@@ -5887,7 +5971,7 @@
       <c r="B46" s="2" t="inlineStr"/>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>沪A68375D</t>
+          <t>沪A67057D</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -5897,7 +5981,7 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:26</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
@@ -5935,12 +6019,12 @@
       <c r="N46" s="2" t="inlineStr"/>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5954,7 +6038,7 @@
       <c r="U46" s="2" t="inlineStr"/>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:26</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
@@ -6003,7 +6087,7 @@
       <c r="B47" s="2" t="inlineStr"/>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>沪A68895D</t>
+          <t>沪A72873D</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -6013,7 +6097,7 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
@@ -6051,12 +6135,12 @@
       <c r="N47" s="2" t="inlineStr"/>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>05:49</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -6070,7 +6154,7 @@
       <c r="U47" s="2" t="inlineStr"/>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
@@ -6119,7 +6203,7 @@
       <c r="B48" s="2" t="inlineStr"/>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>沪A65668D</t>
+          <t>沪A67712D</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -6129,7 +6213,7 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>07:41</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
@@ -6167,12 +6251,12 @@
       <c r="N48" s="2" t="inlineStr"/>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>05:49</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -6186,7 +6270,7 @@
       <c r="U48" s="2" t="inlineStr"/>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>07:41</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
@@ -6235,7 +6319,7 @@
       <c r="B49" s="2" t="inlineStr"/>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>沪A02316D</t>
+          <t>沪A90275D</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -6245,7 +6329,7 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>08:25</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
@@ -6283,12 +6367,12 @@
       <c r="N49" s="2" t="inlineStr"/>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -6302,7 +6386,7 @@
       <c r="U49" s="2" t="inlineStr"/>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>08:25</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
@@ -6351,22 +6435,22 @@
       <c r="B50" s="2" t="inlineStr"/>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>沪A62880D</t>
+          <t>沪A02891D</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E50" s="2" t="inlineStr">
-        <is>
-          <t>08:30</t>
-        </is>
-      </c>
-      <c r="F50" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -6399,12 +6483,12 @@
       <c r="N50" s="2" t="inlineStr"/>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>05:49</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6418,7 +6502,7 @@
       <c r="U50" s="2" t="inlineStr"/>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
@@ -6443,22 +6527,18 @@
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC50" s="2" t="inlineStr">
-        <is>
-          <t>143.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC50" s="2" t="inlineStr"/>
       <c r="AD50" s="2" t="inlineStr">
         <is>
-          <t>2/25</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -6471,22 +6551,22 @@
       <c r="B51" s="2" t="inlineStr"/>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>沪A09172D</t>
+          <t>沪A62981D</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E51" s="2" t="inlineStr">
-        <is>
-          <t>08:40</t>
-        </is>
-      </c>
-      <c r="F51" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -6519,12 +6599,12 @@
       <c r="N51" s="2" t="inlineStr"/>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>05:49</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -6538,7 +6618,7 @@
       <c r="U51" s="2" t="inlineStr"/>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W51" s="2" t="inlineStr">
@@ -6563,22 +6643,18 @@
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC51" s="2" t="inlineStr">
-        <is>
-          <t>124.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC51" s="2" t="inlineStr"/>
       <c r="AD51" s="2" t="inlineStr">
         <is>
-          <t>1/25</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -6591,7 +6667,7 @@
       <c r="B52" s="2" t="inlineStr"/>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>沪A66883D</t>
+          <t>沪A68375D</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
@@ -6601,7 +6677,7 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
@@ -6639,12 +6715,12 @@
       <c r="N52" s="2" t="inlineStr"/>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>05:49</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6658,7 +6734,7 @@
       <c r="U52" s="2" t="inlineStr"/>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
@@ -6683,22 +6759,18 @@
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC52" s="2" t="inlineStr">
-        <is>
-          <t>148.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC52" s="2" t="inlineStr"/>
       <c r="AD52" s="2" t="inlineStr">
         <is>
-          <t>3/25</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -6711,7 +6783,7 @@
       <c r="B53" s="2" t="inlineStr"/>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>沪A05218D</t>
+          <t>沪A68895D</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
@@ -6721,7 +6793,7 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
@@ -6759,12 +6831,12 @@
       <c r="N53" s="2" t="inlineStr"/>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>05:49</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6778,7 +6850,7 @@
       <c r="U53" s="2" t="inlineStr"/>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
@@ -6827,22 +6899,22 @@
       <c r="B54" s="2" t="inlineStr"/>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>沪A57051D</t>
+          <t>沪A65668D</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E54" s="2" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="F54" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -6880,7 +6952,7 @@
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6894,7 +6966,7 @@
       <c r="U54" s="2" t="inlineStr"/>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
@@ -6919,7 +6991,7 @@
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
@@ -6943,22 +7015,22 @@
       <c r="B55" s="2" t="inlineStr"/>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>沪A71572D</t>
+          <t>沪A02316D</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>08:25</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E55" s="2" t="inlineStr">
-        <is>
-          <t>09:10</t>
-        </is>
-      </c>
-      <c r="F55" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -6991,12 +7063,12 @@
       <c r="N55" s="2" t="inlineStr"/>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>05:49</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -7010,7 +7082,7 @@
       <c r="U55" s="2" t="inlineStr"/>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>08:25</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
@@ -7035,7 +7107,7 @@
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
@@ -7053,28 +7125,28 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr"/>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A62880D</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>05:58</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -7107,12 +7179,12 @@
       <c r="N56" s="2" t="inlineStr"/>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>05:48</t>
+          <t>05:49</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -7126,7 +7198,7 @@
       <c r="U56" s="2" t="inlineStr"/>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>05:58</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
@@ -7156,41 +7228,45 @@
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC56" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC56" s="2" t="inlineStr">
+        <is>
+          <t>143.0</t>
+        </is>
+      </c>
       <c r="AD56" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>2/25</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr"/>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>沪A35616D</t>
+          <t>沪A09172D</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -7223,12 +7299,12 @@
       <c r="N57" s="2" t="inlineStr"/>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>05:48</t>
+          <t>05:49</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -7242,7 +7318,7 @@
       <c r="U57" s="2" t="inlineStr"/>
       <c r="V57" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="W57" s="2" t="inlineStr">
@@ -7272,41 +7348,45 @@
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC57" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC57" s="2" t="inlineStr">
+        <is>
+          <t>124.0</t>
+        </is>
+      </c>
       <c r="AD57" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>1/25</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr"/>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>沪A57022D</t>
+          <t>沪A66883D</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
@@ -7339,12 +7419,12 @@
       <c r="N58" s="2" t="inlineStr"/>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>05:48</t>
+          <t>05:49</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -7358,7 +7438,7 @@
       <c r="U58" s="2" t="inlineStr"/>
       <c r="V58" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="W58" s="2" t="inlineStr">
@@ -7388,83 +7468,83 @@
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC58" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC58" s="2" t="inlineStr">
+        <is>
+          <t>146.0</t>
+        </is>
+      </c>
       <c r="AD58" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>3/25</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr"/>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>沪A36809D</t>
+          <t>沪A05218D</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
         <is>
-          <t>92分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr"/>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N59" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N59" s="2" t="inlineStr"/>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr">
@@ -7478,7 +7558,7 @@
       <c r="U59" s="2" t="inlineStr"/>
       <c r="V59" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="W59" s="2" t="inlineStr">
@@ -7488,107 +7568,99 @@
       </c>
       <c r="X59" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y59" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z59" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC59" s="2" t="inlineStr">
-        <is>
-          <t>92.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC59" s="2" t="inlineStr"/>
       <c r="AD59" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr"/>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>沪A61166D</t>
+          <t>沪A57051D</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
-          <t>91分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="2" t="inlineStr"/>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
-        </is>
-      </c>
-      <c r="N60" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N60" s="2" t="inlineStr"/>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>05:49</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -7602,7 +7674,7 @@
       <c r="U60" s="2" t="inlineStr"/>
       <c r="V60" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="W60" s="2" t="inlineStr">
@@ -7612,17 +7684,17 @@
       </c>
       <c r="X60" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y60" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z60" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA60" s="2" t="inlineStr">
@@ -7632,45 +7704,41 @@
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC60" s="2" t="inlineStr">
-        <is>
-          <t>91.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC60" s="2" t="inlineStr"/>
       <c r="AD60" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr"/>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>沪A35172D</t>
+          <t>沪A71572D</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
@@ -7703,12 +7771,12 @@
       <c r="N61" s="2" t="inlineStr"/>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>05:49</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
@@ -7722,7 +7790,7 @@
       <c r="U61" s="2" t="inlineStr"/>
       <c r="V61" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="W61" s="2" t="inlineStr">
@@ -7752,83 +7820,83 @@
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC61" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC61" s="2" t="inlineStr">
+        <is>
+          <t>153.0</t>
+        </is>
+      </c>
       <c r="AD61" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>5/25</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr"/>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>沪A66391D</t>
+          <t>沪A51682D</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>08:17</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>87分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr"/>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N62" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N62" s="2" t="inlineStr"/>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>05:49</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -7842,7 +7910,7 @@
       <c r="U62" s="2" t="inlineStr"/>
       <c r="V62" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="W62" s="2" t="inlineStr">
@@ -7852,17 +7920,17 @@
       </c>
       <c r="X62" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y62" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z62" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA62" s="2" t="inlineStr">
@@ -7872,45 +7940,41 @@
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC62" s="2" t="inlineStr">
-        <is>
-          <t>87.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC62" s="2" t="inlineStr"/>
       <c r="AD62" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr"/>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>沪A35591D</t>
+          <t>沪A11062A</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
@@ -7943,12 +8007,12 @@
       <c r="N63" s="2" t="inlineStr"/>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -7962,7 +8026,7 @@
       <c r="U63" s="2" t="inlineStr"/>
       <c r="V63" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="W63" s="2" t="inlineStr">
@@ -7987,7 +8051,7 @@
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB63" s="2" t="inlineStr">
@@ -7998,77 +8062,73 @@
       <c r="AC63" s="2" t="inlineStr"/>
       <c r="AD63" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr"/>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A37823D</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>08:25</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t>85分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr"/>
       <c r="L64" s="2" t="inlineStr"/>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N64" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N64" s="2" t="inlineStr"/>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
@@ -8082,7 +8142,7 @@
       <c r="U64" s="2" t="inlineStr"/>
       <c r="V64" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="W64" s="2" t="inlineStr">
@@ -8092,17 +8152,17 @@
       </c>
       <c r="X64" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y64" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z64" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA64" s="2" t="inlineStr">
@@ -8117,40 +8177,40 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>160.0</t>
         </is>
       </c>
       <c r="AD64" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>6/25</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr"/>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>沪A51173D</t>
+          <t>沪A70597D</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
@@ -8183,12 +8243,12 @@
       <c r="N65" s="2" t="inlineStr"/>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -8202,7 +8262,7 @@
       <c r="U65" s="2" t="inlineStr"/>
       <c r="V65" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="W65" s="2" t="inlineStr">
@@ -8227,46 +8287,50 @@
       </c>
       <c r="AA65" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB65" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB65" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC65" s="2" t="inlineStr"/>
+      <c r="AC65" s="2" t="inlineStr">
+        <is>
+          <t>161.0</t>
+        </is>
+      </c>
       <c r="AD65" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>7/25</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr"/>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A95621D</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
@@ -8299,12 +8363,12 @@
       <c r="N66" s="2" t="inlineStr"/>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr">
@@ -8318,7 +8382,7 @@
       <c r="U66" s="2" t="inlineStr"/>
       <c r="V66" s="2" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="W66" s="2" t="inlineStr">
@@ -8354,35 +8418,35 @@
       <c r="AC66" s="2" t="inlineStr"/>
       <c r="AD66" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr"/>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>沪A56123D</t>
+          <t>沪A37267D</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
@@ -8415,12 +8479,12 @@
       <c r="N67" s="2" t="inlineStr"/>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
@@ -8434,7 +8498,7 @@
       <c r="U67" s="2" t="inlineStr"/>
       <c r="V67" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="W67" s="2" t="inlineStr">
@@ -8459,46 +8523,50 @@
       </c>
       <c r="AA67" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB67" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB67" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC67" s="2" t="inlineStr"/>
+      <c r="AC67" s="2" t="inlineStr">
+        <is>
+          <t>149.0</t>
+        </is>
+      </c>
       <c r="AD67" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>4/25</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr"/>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A55102D</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
@@ -8531,12 +8599,12 @@
       <c r="N68" s="2" t="inlineStr"/>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q68" s="2" t="inlineStr">
@@ -8550,7 +8618,7 @@
       <c r="U68" s="2" t="inlineStr"/>
       <c r="V68" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="W68" s="2" t="inlineStr">
@@ -8575,7 +8643,7 @@
       </c>
       <c r="AA68" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB68" s="2" t="inlineStr">
@@ -8586,7 +8654,7 @@
       <c r="AC68" s="2" t="inlineStr"/>
       <c r="AD68" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -8599,7 +8667,7 @@
       <c r="B69" s="2" t="inlineStr"/>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>沪A55150D</t>
+          <t>沪A55207D</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
@@ -8609,7 +8677,7 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>05:58</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
@@ -8652,7 +8720,7 @@
       </c>
       <c r="P69" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q69" s="2" t="inlineStr">
@@ -8666,7 +8734,7 @@
       <c r="U69" s="2" t="inlineStr"/>
       <c r="V69" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>05:58</t>
         </is>
       </c>
       <c r="W69" s="2" t="inlineStr">
@@ -8691,18 +8759,22 @@
       </c>
       <c r="AA69" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB69" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB69" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC69" s="2" t="inlineStr"/>
+      <c r="AC69" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
       <c r="AD69" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -8715,7 +8787,7 @@
       <c r="B70" s="2" t="inlineStr"/>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>沪A53629D</t>
+          <t>沪A35616D</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
@@ -8725,7 +8797,7 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
@@ -8763,12 +8835,12 @@
       <c r="N70" s="2" t="inlineStr"/>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>05:48</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q70" s="2" t="inlineStr">
@@ -8782,7 +8854,7 @@
       <c r="U70" s="2" t="inlineStr"/>
       <c r="V70" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W70" s="2" t="inlineStr">
@@ -8807,7 +8879,7 @@
       </c>
       <c r="AA70" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB70" s="2" t="inlineStr">
@@ -8831,22 +8903,22 @@
       <c r="B71" s="2" t="inlineStr"/>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A57022D</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>06:25</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="E71" s="2" t="inlineStr">
-        <is>
-          <t>07:45</t>
-        </is>
-      </c>
-      <c r="F71" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
@@ -8884,7 +8956,7 @@
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q71" s="2" t="inlineStr">
@@ -8898,7 +8970,7 @@
       <c r="U71" s="2" t="inlineStr"/>
       <c r="V71" s="2" t="inlineStr">
         <is>
-          <t>07:45</t>
+          <t>06:25</t>
         </is>
       </c>
       <c r="W71" s="2" t="inlineStr">
@@ -8923,7 +8995,7 @@
       </c>
       <c r="AA71" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB71" s="2" t="inlineStr">
@@ -8947,7 +9019,7 @@
       <c r="B72" s="2" t="inlineStr"/>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>沪A52736D</t>
+          <t>沪A36809D</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
@@ -8957,7 +9029,7 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
@@ -8967,32 +9039,36 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>92分钟</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr"/>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N72" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N72" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -9000,7 +9076,7 @@
       </c>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q72" s="2" t="inlineStr">
@@ -9014,7 +9090,7 @@
       <c r="U72" s="2" t="inlineStr"/>
       <c r="V72" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="W72" s="2" t="inlineStr">
@@ -9024,33 +9100,37 @@
       </c>
       <c r="X72" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z72" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA72" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB72" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB72" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC72" s="2" t="inlineStr"/>
+      <c r="AC72" s="2" t="inlineStr">
+        <is>
+          <t>92.0</t>
+        </is>
+      </c>
       <c r="AD72" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -9063,7 +9143,7 @@
       <c r="B73" s="2" t="inlineStr"/>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>沪A35616D</t>
+          <t>沪A61166D</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
@@ -9073,7 +9153,7 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>07:57</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
@@ -9083,40 +9163,44 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>91分钟</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr"/>
       <c r="L73" s="2" t="inlineStr"/>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N73" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N73" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>05:48</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q73" s="2" t="inlineStr">
@@ -9130,7 +9214,7 @@
       <c r="U73" s="2" t="inlineStr"/>
       <c r="V73" s="2" t="inlineStr">
         <is>
-          <t>07:57</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="W73" s="2" t="inlineStr">
@@ -9140,17 +9224,17 @@
       </c>
       <c r="X73" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z73" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA73" s="2" t="inlineStr">
@@ -9160,13 +9244,17 @@
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC73" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC73" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
       <c r="AD73" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -9179,7 +9267,7 @@
       <c r="B74" s="2" t="inlineStr"/>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>沪A57902D</t>
+          <t>沪A35172D</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
@@ -9189,7 +9277,7 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
@@ -9199,40 +9287,44 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:34</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>104分钟</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="2" t="inlineStr"/>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N74" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N74" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>06:20</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q74" s="2" t="inlineStr">
@@ -9246,7 +9338,7 @@
       <c r="U74" s="2" t="inlineStr"/>
       <c r="V74" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="W74" s="2" t="inlineStr">
@@ -9256,33 +9348,37 @@
       </c>
       <c r="X74" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z74" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA74" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB74" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB74" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC74" s="2" t="inlineStr"/>
+      <c r="AC74" s="2" t="inlineStr">
+        <is>
+          <t>104.0</t>
+        </is>
+      </c>
       <c r="AD74" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -9295,7 +9391,7 @@
       <c r="B75" s="2" t="inlineStr"/>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>沪A57022D</t>
+          <t>沪A66391D</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
@@ -9305,7 +9401,7 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>08:09</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
@@ -9315,40 +9411,44 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:17</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="2" t="inlineStr"/>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N75" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N75" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>05:48</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q75" s="2" t="inlineStr">
@@ -9362,7 +9462,7 @@
       <c r="U75" s="2" t="inlineStr"/>
       <c r="V75" s="2" t="inlineStr">
         <is>
-          <t>08:09</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="W75" s="2" t="inlineStr">
@@ -9372,17 +9472,17 @@
       </c>
       <c r="X75" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z75" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA75" s="2" t="inlineStr">
@@ -9392,13 +9492,17 @@
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC75" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC75" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
       <c r="AD75" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -9411,7 +9515,7 @@
       <c r="B76" s="2" t="inlineStr"/>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>沪A61166D</t>
+          <t>沪A35591D</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
@@ -9421,7 +9525,7 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
@@ -9464,7 +9568,7 @@
       </c>
       <c r="P76" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q76" s="2" t="inlineStr">
@@ -9478,7 +9582,7 @@
       <c r="U76" s="2" t="inlineStr"/>
       <c r="V76" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="W76" s="2" t="inlineStr">
@@ -9508,17 +9612,13 @@
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC76" s="2" t="inlineStr">
-        <is>
-          <t>91.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC76" s="2" t="inlineStr"/>
       <c r="AD76" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -9531,52 +9631,56 @@
       <c r="B77" s="2" t="inlineStr"/>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>沪A66391D</t>
+          <t>沪A56630D</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="E77" s="2" t="inlineStr">
-        <is>
-          <t>08:30</t>
-        </is>
-      </c>
-      <c r="F77" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:25</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="2" t="inlineStr"/>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N77" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -9584,7 +9688,7 @@
       </c>
       <c r="P77" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q77" s="2" t="inlineStr">
@@ -9598,7 +9702,7 @@
       <c r="U77" s="2" t="inlineStr"/>
       <c r="V77" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="W77" s="2" t="inlineStr">
@@ -9608,17 +9712,17 @@
       </c>
       <c r="X77" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z77" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA77" s="2" t="inlineStr">
@@ -9633,12 +9737,12 @@
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AD77" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -9651,60 +9755,64 @@
       <c r="B78" s="2" t="inlineStr"/>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>沪A36809D</t>
+          <t>沪A51173D</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="E78" s="2" t="inlineStr">
-        <is>
-          <t>08:33</t>
-        </is>
-      </c>
-      <c r="F78" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:54</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>104分钟</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr"/>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N78" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q78" s="2" t="inlineStr">
@@ -9718,7 +9826,7 @@
       <c r="U78" s="2" t="inlineStr"/>
       <c r="V78" s="2" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>07:10</t>
         </is>
       </c>
       <c r="W78" s="2" t="inlineStr">
@@ -9728,17 +9836,17 @@
       </c>
       <c r="X78" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z78" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA78" s="2" t="inlineStr">
@@ -9753,12 +9861,12 @@
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>104.0</t>
         </is>
       </c>
       <c r="AD78" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -9771,7 +9879,7 @@
       <c r="B79" s="2" t="inlineStr"/>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>沪A36930D</t>
+          <t>沪A59117D</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
@@ -9781,7 +9889,7 @@
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>07:15</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
@@ -9791,40 +9899,44 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>91分钟</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr"/>
       <c r="L79" s="2" t="inlineStr"/>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N79" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N79" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>07:40</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q79" s="2" t="inlineStr">
@@ -9838,7 +9950,7 @@
       <c r="U79" s="2" t="inlineStr"/>
       <c r="V79" s="2" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>07:15</t>
         </is>
       </c>
       <c r="W79" s="2" t="inlineStr">
@@ -9848,33 +9960,37 @@
       </c>
       <c r="X79" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z79" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA79" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB79" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB79" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC79" s="2" t="inlineStr"/>
+      <c r="AC79" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
       <c r="AD79" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -9887,60 +10003,64 @@
       <c r="B80" s="2" t="inlineStr"/>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>沪A35172D</t>
+          <t>沪A56123D</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="E80" s="2" t="inlineStr">
-        <is>
-          <t>08:45</t>
-        </is>
-      </c>
-      <c r="F80" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>103分钟</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr"/>
       <c r="L80" s="2" t="inlineStr"/>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N80" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N80" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q80" s="2" t="inlineStr">
@@ -9954,7 +10074,7 @@
       <c r="U80" s="2" t="inlineStr"/>
       <c r="V80" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="W80" s="2" t="inlineStr">
@@ -9964,17 +10084,17 @@
       </c>
       <c r="X80" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z80" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA80" s="2" t="inlineStr">
@@ -9984,13 +10104,17 @@
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC80" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC80" s="2" t="inlineStr">
+        <is>
+          <t>103.0</t>
+        </is>
+      </c>
       <c r="AD80" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -10003,60 +10127,64 @@
       <c r="B81" s="2" t="inlineStr"/>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A35186D</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="E81" s="2" t="inlineStr">
-        <is>
-          <t>08:45</t>
-        </is>
-      </c>
-      <c r="F81" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:58</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr"/>
       <c r="L81" s="2" t="inlineStr"/>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N81" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N81" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q81" s="2" t="inlineStr">
@@ -10070,7 +10198,7 @@
       <c r="U81" s="2" t="inlineStr"/>
       <c r="V81" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W81" s="2" t="inlineStr">
@@ -10080,17 +10208,17 @@
       </c>
       <c r="X81" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z81" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA81" s="2" t="inlineStr">
@@ -10105,12 +10233,12 @@
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AD81" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -10123,7 +10251,7 @@
       <c r="B82" s="2" t="inlineStr"/>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A55150D</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
@@ -10133,7 +10261,7 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
@@ -10171,12 +10299,12 @@
       <c r="N82" s="2" t="inlineStr"/>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>05:48</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q82" s="2" t="inlineStr">
@@ -10190,7 +10318,7 @@
       <c r="U82" s="2" t="inlineStr"/>
       <c r="V82" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W82" s="2" t="inlineStr">
@@ -10227,6 +10355,2630 @@
       <c r="AD82" s="2" t="inlineStr">
         <is>
           <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr"/>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>沪A53629D</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>09:14</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr">
+        <is>
+          <t>92分钟</t>
+        </is>
+      </c>
+      <c r="K83" s="2" t="inlineStr"/>
+      <c r="L83" s="2" t="inlineStr"/>
+      <c r="M83" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N83" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O83" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="P83" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="Q83" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R83" s="2" t="inlineStr"/>
+      <c r="S83" s="2" t="inlineStr"/>
+      <c r="T83" s="2" t="inlineStr"/>
+      <c r="U83" s="2" t="inlineStr"/>
+      <c r="V83" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="W83" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X83" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y83" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z83" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA83" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB83" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC83" s="2" t="inlineStr">
+        <is>
+          <t>92.0</t>
+        </is>
+      </c>
+      <c r="AD83" s="2" t="inlineStr">
+        <is>
+          <t>8/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr"/>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>07:45</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>09:14</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr">
+        <is>
+          <t>89分钟</t>
+        </is>
+      </c>
+      <c r="K84" s="2" t="inlineStr"/>
+      <c r="L84" s="2" t="inlineStr"/>
+      <c r="M84" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N84" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>05:48</t>
+        </is>
+      </c>
+      <c r="P84" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q84" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R84" s="2" t="inlineStr"/>
+      <c r="S84" s="2" t="inlineStr"/>
+      <c r="T84" s="2" t="inlineStr"/>
+      <c r="U84" s="2" t="inlineStr"/>
+      <c r="V84" s="2" t="inlineStr">
+        <is>
+          <t>07:45</t>
+        </is>
+      </c>
+      <c r="W84" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X84" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y84" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z84" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA84" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB84" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC84" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
+      <c r="AD84" s="2" t="inlineStr">
+        <is>
+          <t>4/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr"/>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>09:24</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr">
+        <is>
+          <t>90分钟</t>
+        </is>
+      </c>
+      <c r="K85" s="2" t="inlineStr"/>
+      <c r="L85" s="2" t="inlineStr"/>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N85" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P85" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q85" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R85" s="2" t="inlineStr"/>
+      <c r="S85" s="2" t="inlineStr"/>
+      <c r="T85" s="2" t="inlineStr"/>
+      <c r="U85" s="2" t="inlineStr"/>
+      <c r="V85" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="W85" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X85" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y85" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z85" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA85" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB85" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC85" s="2" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="AD85" s="2" t="inlineStr">
+        <is>
+          <t>5/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr"/>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>07:57</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K86" s="2" t="inlineStr"/>
+      <c r="L86" s="2" t="inlineStr"/>
+      <c r="M86" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N86" s="2" t="inlineStr"/>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>05:48</t>
+        </is>
+      </c>
+      <c r="P86" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q86" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R86" s="2" t="inlineStr"/>
+      <c r="S86" s="2" t="inlineStr"/>
+      <c r="T86" s="2" t="inlineStr"/>
+      <c r="U86" s="2" t="inlineStr"/>
+      <c r="V86" s="2" t="inlineStr">
+        <is>
+          <t>07:57</t>
+        </is>
+      </c>
+      <c r="W86" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X86" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z86" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA86" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB86" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC86" s="2" t="inlineStr"/>
+      <c r="AD86" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr"/>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>沪A57902D</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K87" s="2" t="inlineStr"/>
+      <c r="L87" s="2" t="inlineStr"/>
+      <c r="M87" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N87" s="2" t="inlineStr"/>
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="P87" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q87" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R87" s="2" t="inlineStr"/>
+      <c r="S87" s="2" t="inlineStr"/>
+      <c r="T87" s="2" t="inlineStr"/>
+      <c r="U87" s="2" t="inlineStr"/>
+      <c r="V87" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="W87" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X87" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z87" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA87" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB87" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC87" s="2" t="inlineStr"/>
+      <c r="AD87" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr"/>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>08:09</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K88" s="2" t="inlineStr"/>
+      <c r="L88" s="2" t="inlineStr"/>
+      <c r="M88" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N88" s="2" t="inlineStr"/>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>05:48</t>
+        </is>
+      </c>
+      <c r="P88" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q88" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R88" s="2" t="inlineStr"/>
+      <c r="S88" s="2" t="inlineStr"/>
+      <c r="T88" s="2" t="inlineStr"/>
+      <c r="U88" s="2" t="inlineStr"/>
+      <c r="V88" s="2" t="inlineStr">
+        <is>
+          <t>08:09</t>
+        </is>
+      </c>
+      <c r="W88" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X88" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z88" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA88" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB88" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC88" s="2" t="inlineStr"/>
+      <c r="AD88" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr"/>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K89" s="2" t="inlineStr"/>
+      <c r="L89" s="2" t="inlineStr"/>
+      <c r="M89" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N89" s="2" t="inlineStr"/>
+      <c r="O89" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P89" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q89" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R89" s="2" t="inlineStr"/>
+      <c r="S89" s="2" t="inlineStr"/>
+      <c r="T89" s="2" t="inlineStr"/>
+      <c r="U89" s="2" t="inlineStr"/>
+      <c r="V89" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="W89" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X89" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z89" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA89" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB89" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC89" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
+      <c r="AD89" s="2" t="inlineStr">
+        <is>
+          <t>6/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr"/>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K90" s="2" t="inlineStr"/>
+      <c r="L90" s="2" t="inlineStr"/>
+      <c r="M90" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N90" s="2" t="inlineStr"/>
+      <c r="O90" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P90" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q90" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R90" s="2" t="inlineStr"/>
+      <c r="S90" s="2" t="inlineStr"/>
+      <c r="T90" s="2" t="inlineStr"/>
+      <c r="U90" s="2" t="inlineStr"/>
+      <c r="V90" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="W90" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X90" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z90" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA90" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB90" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC90" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
+      <c r="AD90" s="2" t="inlineStr">
+        <is>
+          <t>2/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr"/>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>08:33</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K91" s="2" t="inlineStr"/>
+      <c r="L91" s="2" t="inlineStr"/>
+      <c r="M91" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N91" s="2" t="inlineStr"/>
+      <c r="O91" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P91" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q91" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R91" s="2" t="inlineStr"/>
+      <c r="S91" s="2" t="inlineStr"/>
+      <c r="T91" s="2" t="inlineStr"/>
+      <c r="U91" s="2" t="inlineStr"/>
+      <c r="V91" s="2" t="inlineStr">
+        <is>
+          <t>08:33</t>
+        </is>
+      </c>
+      <c r="W91" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X91" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z91" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA91" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB91" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC91" s="2" t="inlineStr">
+        <is>
+          <t>92.0</t>
+        </is>
+      </c>
+      <c r="AD91" s="2" t="inlineStr">
+        <is>
+          <t>8/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr"/>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K92" s="2" t="inlineStr"/>
+      <c r="L92" s="2" t="inlineStr"/>
+      <c r="M92" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N92" s="2" t="inlineStr"/>
+      <c r="O92" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="P92" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q92" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R92" s="2" t="inlineStr"/>
+      <c r="S92" s="2" t="inlineStr"/>
+      <c r="T92" s="2" t="inlineStr"/>
+      <c r="U92" s="2" t="inlineStr"/>
+      <c r="V92" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="W92" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X92" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z92" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA92" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB92" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC92" s="2" t="inlineStr">
+        <is>
+          <t>104.0</t>
+        </is>
+      </c>
+      <c r="AD92" s="2" t="inlineStr">
+        <is>
+          <t>11/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr"/>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>沪A36930D</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K93" s="2" t="inlineStr"/>
+      <c r="L93" s="2" t="inlineStr"/>
+      <c r="M93" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N93" s="2" t="inlineStr"/>
+      <c r="O93" s="2" t="inlineStr">
+        <is>
+          <t>07:40</t>
+        </is>
+      </c>
+      <c r="P93" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q93" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R93" s="2" t="inlineStr"/>
+      <c r="S93" s="2" t="inlineStr"/>
+      <c r="T93" s="2" t="inlineStr"/>
+      <c r="U93" s="2" t="inlineStr"/>
+      <c r="V93" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="W93" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X93" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z93" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA93" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB93" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC93" s="2" t="inlineStr"/>
+      <c r="AD93" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr"/>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K94" s="2" t="inlineStr"/>
+      <c r="L94" s="2" t="inlineStr"/>
+      <c r="M94" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N94" s="2" t="inlineStr"/>
+      <c r="O94" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P94" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q94" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R94" s="2" t="inlineStr"/>
+      <c r="S94" s="2" t="inlineStr"/>
+      <c r="T94" s="2" t="inlineStr"/>
+      <c r="U94" s="2" t="inlineStr"/>
+      <c r="V94" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="W94" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X94" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z94" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA94" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB94" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC94" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
+      <c r="AD94" s="2" t="inlineStr">
+        <is>
+          <t>1/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr"/>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>08:57</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K95" s="2" t="inlineStr"/>
+      <c r="L95" s="2" t="inlineStr"/>
+      <c r="M95" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N95" s="2" t="inlineStr"/>
+      <c r="O95" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P95" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q95" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R95" s="2" t="inlineStr"/>
+      <c r="S95" s="2" t="inlineStr"/>
+      <c r="T95" s="2" t="inlineStr"/>
+      <c r="U95" s="2" t="inlineStr"/>
+      <c r="V95" s="2" t="inlineStr">
+        <is>
+          <t>08:57</t>
+        </is>
+      </c>
+      <c r="W95" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X95" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z95" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA95" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB95" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC95" s="2" t="inlineStr"/>
+      <c r="AD95" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr"/>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K96" s="2" t="inlineStr"/>
+      <c r="L96" s="2" t="inlineStr"/>
+      <c r="M96" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N96" s="2" t="inlineStr"/>
+      <c r="O96" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="P96" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q96" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R96" s="2" t="inlineStr"/>
+      <c r="S96" s="2" t="inlineStr"/>
+      <c r="T96" s="2" t="inlineStr"/>
+      <c r="U96" s="2" t="inlineStr"/>
+      <c r="V96" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="W96" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X96" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z96" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA96" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB96" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC96" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
+      <c r="AD96" s="2" t="inlineStr">
+        <is>
+          <t>6/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr"/>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K97" s="2" t="inlineStr"/>
+      <c r="L97" s="2" t="inlineStr"/>
+      <c r="M97" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N97" s="2" t="inlineStr"/>
+      <c r="O97" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="P97" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q97" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R97" s="2" t="inlineStr"/>
+      <c r="S97" s="2" t="inlineStr"/>
+      <c r="T97" s="2" t="inlineStr"/>
+      <c r="U97" s="2" t="inlineStr"/>
+      <c r="V97" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="W97" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X97" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z97" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA97" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB97" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC97" s="2" t="inlineStr">
+        <is>
+          <t>104.0</t>
+        </is>
+      </c>
+      <c r="AD97" s="2" t="inlineStr">
+        <is>
+          <t>11/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr"/>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K98" s="2" t="inlineStr"/>
+      <c r="L98" s="2" t="inlineStr"/>
+      <c r="M98" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N98" s="2" t="inlineStr"/>
+      <c r="O98" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="P98" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q98" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R98" s="2" t="inlineStr"/>
+      <c r="S98" s="2" t="inlineStr"/>
+      <c r="T98" s="2" t="inlineStr"/>
+      <c r="U98" s="2" t="inlineStr"/>
+      <c r="V98" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="W98" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X98" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z98" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA98" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB98" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC98" s="2" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
+      <c r="AD98" s="2" t="inlineStr">
+        <is>
+          <t>3/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr"/>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K99" s="2" t="inlineStr"/>
+      <c r="L99" s="2" t="inlineStr"/>
+      <c r="M99" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N99" s="2" t="inlineStr"/>
+      <c r="O99" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="P99" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q99" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R99" s="2" t="inlineStr"/>
+      <c r="S99" s="2" t="inlineStr"/>
+      <c r="T99" s="2" t="inlineStr"/>
+      <c r="U99" s="2" t="inlineStr"/>
+      <c r="V99" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="W99" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X99" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z99" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA99" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB99" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC99" s="2" t="inlineStr">
+        <is>
+          <t>103.0</t>
+        </is>
+      </c>
+      <c r="AD99" s="2" t="inlineStr">
+        <is>
+          <t>10/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr"/>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K100" s="2" t="inlineStr"/>
+      <c r="L100" s="2" t="inlineStr"/>
+      <c r="M100" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N100" s="2" t="inlineStr"/>
+      <c r="O100" s="2" t="inlineStr">
+        <is>
+          <t>05:48</t>
+        </is>
+      </c>
+      <c r="P100" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q100" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R100" s="2" t="inlineStr"/>
+      <c r="S100" s="2" t="inlineStr"/>
+      <c r="T100" s="2" t="inlineStr"/>
+      <c r="U100" s="2" t="inlineStr"/>
+      <c r="V100" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="W100" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X100" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z100" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA100" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB100" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC100" s="2" t="inlineStr"/>
+      <c r="AD100" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr"/>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K101" s="2" t="inlineStr"/>
+      <c r="L101" s="2" t="inlineStr"/>
+      <c r="M101" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N101" s="2" t="inlineStr"/>
+      <c r="O101" s="2" t="inlineStr">
+        <is>
+          <t>05:48</t>
+        </is>
+      </c>
+      <c r="P101" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q101" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R101" s="2" t="inlineStr"/>
+      <c r="S101" s="2" t="inlineStr"/>
+      <c r="T101" s="2" t="inlineStr"/>
+      <c r="U101" s="2" t="inlineStr"/>
+      <c r="V101" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="W101" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X101" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z101" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA101" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB101" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC101" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
+      <c r="AD101" s="2" t="inlineStr">
+        <is>
+          <t>4/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr"/>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K102" s="2" t="inlineStr"/>
+      <c r="L102" s="2" t="inlineStr"/>
+      <c r="M102" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N102" s="2" t="inlineStr"/>
+      <c r="O102" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P102" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q102" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R102" s="2" t="inlineStr"/>
+      <c r="S102" s="2" t="inlineStr"/>
+      <c r="T102" s="2" t="inlineStr"/>
+      <c r="U102" s="2" t="inlineStr"/>
+      <c r="V102" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="W102" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X102" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z102" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA102" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB102" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC102" s="2" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="AD102" s="2" t="inlineStr">
+        <is>
+          <t>5/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr"/>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K103" s="2" t="inlineStr"/>
+      <c r="L103" s="2" t="inlineStr"/>
+      <c r="M103" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N103" s="2" t="inlineStr"/>
+      <c r="O103" s="2" t="inlineStr">
+        <is>
+          <t>05:48</t>
+        </is>
+      </c>
+      <c r="P103" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q103" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R103" s="2" t="inlineStr"/>
+      <c r="S103" s="2" t="inlineStr"/>
+      <c r="T103" s="2" t="inlineStr"/>
+      <c r="U103" s="2" t="inlineStr"/>
+      <c r="V103" s="2" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="W103" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X103" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z103" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA103" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB103" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC103" s="2" t="inlineStr"/>
+      <c r="AD103" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr"/>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K104" s="2" t="inlineStr"/>
+      <c r="L104" s="2" t="inlineStr"/>
+      <c r="M104" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N104" s="2" t="inlineStr"/>
+      <c r="O104" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P104" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q104" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R104" s="2" t="inlineStr"/>
+      <c r="S104" s="2" t="inlineStr"/>
+      <c r="T104" s="2" t="inlineStr"/>
+      <c r="U104" s="2" t="inlineStr"/>
+      <c r="V104" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="W104" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X104" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z104" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA104" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB104" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC104" s="2" t="inlineStr">
+        <is>
+          <t>92.0</t>
+        </is>
+      </c>
+      <c r="AD104" s="2" t="inlineStr">
+        <is>
+          <t>8/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-13-operations.xlsx
+++ b/data/export/2026-10-13-operations.xlsx
@@ -680,7 +680,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -724,17 +724,17 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>77.8</t>
         </is>
       </c>
       <c r="AD2" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -928,7 +928,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -972,17 +972,17 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AD4" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
@@ -1672,7 +1672,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="AD11" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -2040,7 +2040,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -2084,17 +2084,17 @@
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>77.8</t>
         </is>
       </c>
       <c r="AD13" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -2164,7 +2164,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2208,12 +2208,12 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>78.9</t>
         </is>
       </c>
       <c r="AD14" s="2" t="inlineStr">
@@ -2342,7 +2342,7 @@
       </c>
       <c r="AD15" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -2412,7 +2412,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2456,17 +2456,17 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AD16" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -3032,7 +3032,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
@@ -3404,7 +3404,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3582,7 +3582,7 @@
       </c>
       <c r="AD25" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -3776,7 +3776,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3820,17 +3820,17 @@
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>77.8</t>
         </is>
       </c>
       <c r="AD27" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -3900,7 +3900,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3944,12 +3944,12 @@
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>78.9</t>
         </is>
       </c>
       <c r="AD28" s="2" t="inlineStr">
@@ -4078,7 +4078,7 @@
       </c>
       <c r="AD29" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -4148,7 +4148,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -4192,17 +4192,17 @@
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AD30" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -4768,7 +4768,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4812,7 +4812,7 @@
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
@@ -5016,7 +5016,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -5194,7 +5194,7 @@
       </c>
       <c r="AD38" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -5308,17 +5308,17 @@
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>77.8</t>
         </is>
       </c>
       <c r="AD39" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -5388,7 +5388,7 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -5432,12 +5432,12 @@
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>78.9</t>
         </is>
       </c>
       <c r="AD40" s="2" t="inlineStr">
@@ -5512,7 +5512,7 @@
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5556,17 +5556,17 @@
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AD41" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -5690,7 +5690,7 @@
       </c>
       <c r="AD42" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -6004,7 +6004,7 @@
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -6048,7 +6048,7 @@
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
@@ -6128,7 +6128,7 @@
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -6376,7 +6376,7 @@
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -6420,12 +6420,12 @@
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>78.9</t>
         </is>
       </c>
       <c r="AD48" s="2" t="inlineStr">
@@ -6678,7 +6678,7 @@
       </c>
       <c r="AD50" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -7298,7 +7298,7 @@
       </c>
       <c r="AD55" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -7368,7 +7368,7 @@
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -7412,17 +7412,17 @@
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>77.8</t>
         </is>
       </c>
       <c r="AD56" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -7864,7 +7864,7 @@
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -7908,17 +7908,17 @@
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AD60" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -8112,7 +8112,7 @@
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -8156,7 +8156,7 @@
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
@@ -8290,7 +8290,7 @@
       </c>
       <c r="AD63" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -8484,7 +8484,7 @@
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -8528,17 +8528,17 @@
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>77.8</t>
         </is>
       </c>
       <c r="AD65" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -8608,7 +8608,7 @@
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr">
@@ -8732,7 +8732,7 @@
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
@@ -8776,12 +8776,12 @@
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>78.9</t>
         </is>
       </c>
       <c r="AD67" s="2" t="inlineStr">
@@ -9228,7 +9228,7 @@
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q71" s="2" t="inlineStr">
@@ -9272,17 +9272,17 @@
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AD71" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -9406,7 +9406,7 @@
       </c>
       <c r="AD72" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -9600,7 +9600,7 @@
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q74" s="2" t="inlineStr">
@@ -9644,7 +9644,7 @@
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
@@ -10096,7 +10096,7 @@
       </c>
       <c r="P78" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q78" s="2" t="inlineStr">
@@ -10220,7 +10220,7 @@
       </c>
       <c r="P79" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q79" s="2" t="inlineStr">
@@ -10264,12 +10264,12 @@
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>78.9</t>
         </is>
       </c>
       <c r="AD79" s="2" t="inlineStr">
@@ -10398,7 +10398,7 @@
       </c>
       <c r="AD80" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -10592,7 +10592,7 @@
       </c>
       <c r="P82" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="Q82" s="2" t="inlineStr">
@@ -10636,17 +10636,17 @@
       </c>
       <c r="AB82" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>77.8</t>
         </is>
       </c>
       <c r="AD82" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -10894,7 +10894,7 @@
       </c>
       <c r="AD84" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -10964,7 +10964,7 @@
       </c>
       <c r="P85" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q85" s="2" t="inlineStr">
@@ -11008,17 +11008,17 @@
       </c>
       <c r="AB85" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AD85" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -11336,7 +11336,7 @@
       </c>
       <c r="P88" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q88" s="2" t="inlineStr">
@@ -11380,7 +11380,7 @@
       </c>
       <c r="AB88" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC88" s="2" t="inlineStr">
@@ -11584,7 +11584,7 @@
       </c>
       <c r="P90" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q90" s="2" t="inlineStr">
@@ -11758,7 +11758,7 @@
       </c>
       <c r="AD91" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -11791,32 +11791,36 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:07</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr"/>
       <c r="L92" s="2" t="inlineStr"/>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N92" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N92" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
           <t>05:50</t>
@@ -11824,7 +11828,7 @@
       </c>
       <c r="P92" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="Q92" s="2" t="inlineStr">
@@ -11848,17 +11852,17 @@
       </c>
       <c r="X92" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z92" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA92" s="2" t="inlineStr">
@@ -11868,17 +11872,17 @@
       </c>
       <c r="AB92" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>77.8</t>
         </is>
       </c>
       <c r="AD92" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -11911,32 +11915,36 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:05</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>70分钟</t>
         </is>
       </c>
       <c r="K93" s="2" t="inlineStr"/>
       <c r="L93" s="2" t="inlineStr"/>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N93" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N93" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
           <t>07:02</t>
@@ -11944,7 +11952,7 @@
       </c>
       <c r="P93" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q93" s="2" t="inlineStr">
@@ -11968,17 +11976,17 @@
       </c>
       <c r="X93" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z93" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA93" s="2" t="inlineStr">
@@ -11988,12 +11996,12 @@
       </c>
       <c r="AB93" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>78.9</t>
         </is>
       </c>
       <c r="AD93" s="2" t="inlineStr">
@@ -12031,32 +12039,36 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:23</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr"/>
       <c r="L94" s="2" t="inlineStr"/>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N94" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N94" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
           <t>05:50</t>
@@ -12064,7 +12076,7 @@
       </c>
       <c r="P94" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q94" s="2" t="inlineStr">
@@ -12088,17 +12100,17 @@
       </c>
       <c r="X94" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z94" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA94" s="2" t="inlineStr">
@@ -12108,17 +12120,17 @@
       </c>
       <c r="AB94" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC94" s="2" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AD94" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -12151,32 +12163,36 @@
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="K95" s="2" t="inlineStr"/>
       <c r="L95" s="2" t="inlineStr"/>
       <c r="M95" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N95" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N95" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
           <t>06:12</t>
@@ -12184,7 +12200,7 @@
       </c>
       <c r="P95" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q95" s="2" t="inlineStr">
@@ -12208,17 +12224,17 @@
       </c>
       <c r="X95" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z95" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA95" s="2" t="inlineStr">
@@ -12228,7 +12244,7 @@
       </c>
       <c r="AB95" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC95" s="2" t="inlineStr">
@@ -12304,7 +12320,7 @@
       </c>
       <c r="P96" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q96" s="2" t="inlineStr">
@@ -12424,7 +12440,7 @@
       </c>
       <c r="P97" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q97" s="2" t="inlineStr">
@@ -12468,12 +12484,12 @@
       </c>
       <c r="AB97" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC97" s="2" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>78.9</t>
         </is>
       </c>
       <c r="AD97" s="2" t="inlineStr">
@@ -12548,7 +12564,7 @@
       </c>
       <c r="P98" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q98" s="2" t="inlineStr">
@@ -12592,17 +12608,17 @@
       </c>
       <c r="AB98" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC98" s="2" t="inlineStr">
         <is>
-          <t>138.7</t>
+          <t>135.8</t>
         </is>
       </c>
       <c r="AD98" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -12726,7 +12742,7 @@
       </c>
       <c r="AD99" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -12792,7 +12808,7 @@
       </c>
       <c r="P100" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q100" s="2" t="inlineStr">
@@ -12836,17 +12852,17 @@
       </c>
       <c r="AB100" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC100" s="2" t="inlineStr">
         <is>
-          <t>148.0</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AD100" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -12970,7 +12986,7 @@
       </c>
       <c r="AD101" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -13090,7 +13106,7 @@
       </c>
       <c r="AD102" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -13416,7 +13432,7 @@
       </c>
       <c r="P105" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q105" s="2" t="inlineStr">
@@ -13594,7 +13610,7 @@
       </c>
       <c r="AD106" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -13718,7 +13734,7 @@
       </c>
       <c r="AD107" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -13842,7 +13858,7 @@
       </c>
       <c r="AD108" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -13908,7 +13924,7 @@
       </c>
       <c r="P109" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q109" s="2" t="inlineStr">
@@ -13952,12 +13968,12 @@
       </c>
       <c r="AB109" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC109" s="2" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>142.0</t>
         </is>
       </c>
       <c r="AD109" s="2" t="inlineStr">
@@ -14032,7 +14048,7 @@
       </c>
       <c r="P110" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q110" s="2" t="inlineStr">
@@ -14156,7 +14172,7 @@
       </c>
       <c r="P111" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q111" s="2" t="inlineStr">
@@ -14200,12 +14216,12 @@
       </c>
       <c r="AB111" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC111" s="2" t="inlineStr">
         <is>
-          <t>157.5</t>
+          <t>150.0</t>
         </is>
       </c>
       <c r="AD111" s="2" t="inlineStr">
@@ -14276,7 +14292,7 @@
       </c>
       <c r="P112" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q112" s="2" t="inlineStr">
@@ -14330,7 +14346,7 @@
       </c>
       <c r="AD112" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -14400,7 +14416,7 @@
       </c>
       <c r="P113" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q113" s="2" t="inlineStr">
@@ -14444,17 +14460,17 @@
       </c>
       <c r="AB113" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC113" s="2" t="inlineStr">
         <is>
-          <t>139.3</t>
+          <t>137.5</t>
         </is>
       </c>
       <c r="AD113" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -14574,7 +14590,7 @@
       </c>
       <c r="AD114" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -14644,7 +14660,7 @@
       </c>
       <c r="P115" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q115" s="2" t="inlineStr">
@@ -14698,7 +14714,7 @@
       </c>
       <c r="AD115" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -14768,7 +14784,7 @@
       </c>
       <c r="P116" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q116" s="2" t="inlineStr">
@@ -14822,7 +14838,7 @@
       </c>
       <c r="AD116" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -14892,7 +14908,7 @@
       </c>
       <c r="P117" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q117" s="2" t="inlineStr">
@@ -14936,17 +14952,17 @@
       </c>
       <c r="AB117" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC117" s="2" t="inlineStr">
         <is>
-          <t>141.5</t>
+          <t>143.3</t>
         </is>
       </c>
       <c r="AD117" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -15070,7 +15086,7 @@
       </c>
       <c r="AD118" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -15190,7 +15206,7 @@
       </c>
       <c r="AD119" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -15384,7 +15400,7 @@
       </c>
       <c r="P121" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q121" s="2" t="inlineStr">
@@ -15438,7 +15454,7 @@
       </c>
       <c r="AD121" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -15558,7 +15574,7 @@
       </c>
       <c r="AD122" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -15628,7 +15644,7 @@
       </c>
       <c r="P123" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q123" s="2" t="inlineStr">
@@ -15672,17 +15688,17 @@
       </c>
       <c r="AB123" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC123" s="2" t="inlineStr">
         <is>
-          <t>138.7</t>
+          <t>135.8</t>
         </is>
       </c>
       <c r="AD123" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -15802,7 +15818,7 @@
       </c>
       <c r="AD124" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -15868,7 +15884,7 @@
       </c>
       <c r="P125" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q125" s="2" t="inlineStr">
@@ -15922,7 +15938,7 @@
       </c>
       <c r="AD125" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -15988,7 +16004,7 @@
       </c>
       <c r="P126" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q126" s="2" t="inlineStr">
@@ -16032,17 +16048,17 @@
       </c>
       <c r="AB126" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC126" s="2" t="inlineStr">
         <is>
-          <t>148.0</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AD126" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -16290,7 +16306,7 @@
       </c>
       <c r="AD128" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -16488,7 +16504,7 @@
       </c>
       <c r="P130" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q130" s="2" t="inlineStr">
@@ -16666,7 +16682,7 @@
       </c>
       <c r="AD131" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -16790,7 +16806,7 @@
       </c>
       <c r="AD132" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -16914,7 +16930,7 @@
       </c>
       <c r="AD133" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -16984,7 +17000,7 @@
       </c>
       <c r="P134" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q134" s="2" t="inlineStr">
@@ -17028,12 +17044,12 @@
       </c>
       <c r="AB134" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC134" s="2" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>142.0</t>
         </is>
       </c>
       <c r="AD134" s="2" t="inlineStr">
@@ -17104,7 +17120,7 @@
       </c>
       <c r="P135" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q135" s="2" t="inlineStr">
@@ -17148,12 +17164,12 @@
       </c>
       <c r="AB135" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC135" s="2" t="inlineStr">
         <is>
-          <t>157.5</t>
+          <t>150.0</t>
         </is>
       </c>
       <c r="AD135" s="2" t="inlineStr">
@@ -17228,7 +17244,7 @@
       </c>
       <c r="P136" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q136" s="2" t="inlineStr">
@@ -17352,7 +17368,7 @@
       </c>
       <c r="P137" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q137" s="2" t="inlineStr">
@@ -17396,17 +17412,17 @@
       </c>
       <c r="AB137" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC137" s="2" t="inlineStr">
         <is>
-          <t>139.3</t>
+          <t>137.5</t>
         </is>
       </c>
       <c r="AD137" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -17476,7 +17492,7 @@
       </c>
       <c r="P138" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q138" s="2" t="inlineStr">
@@ -17530,7 +17546,7 @@
       </c>
       <c r="AD138" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -17654,7 +17670,7 @@
       </c>
       <c r="AD139" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -17724,7 +17740,7 @@
       </c>
       <c r="P140" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q140" s="2" t="inlineStr">
@@ -17778,7 +17794,7 @@
       </c>
       <c r="AD140" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -17848,7 +17864,7 @@
       </c>
       <c r="P141" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q141" s="2" t="inlineStr">
@@ -17892,17 +17908,17 @@
       </c>
       <c r="AB141" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC141" s="2" t="inlineStr">
         <is>
-          <t>141.5</t>
+          <t>143.3</t>
         </is>
       </c>
       <c r="AD141" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -17972,7 +17988,7 @@
       </c>
       <c r="P142" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q142" s="2" t="inlineStr">
@@ -18026,7 +18042,7 @@
       </c>
       <c r="AD142" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -18150,7 +18166,7 @@
       </c>
       <c r="AD143" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -18270,7 +18286,7 @@
       </c>
       <c r="AD144" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -18340,7 +18356,7 @@
       </c>
       <c r="P145" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q145" s="2" t="inlineStr">
@@ -18394,7 +18410,7 @@
       </c>
       <c r="AD145" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -18588,7 +18604,7 @@
       </c>
       <c r="P147" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q147" s="2" t="inlineStr">
@@ -18642,7 +18658,7 @@
       </c>
       <c r="AD147" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -18766,7 +18782,7 @@
       </c>
       <c r="AD148" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -18890,7 +18906,7 @@
       </c>
       <c r="AD149" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -18956,7 +18972,7 @@
       </c>
       <c r="P150" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q150" s="2" t="inlineStr">
@@ -19270,7 +19286,7 @@
       </c>
       <c r="AD152" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -19340,7 +19356,7 @@
       </c>
       <c r="P153" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q153" s="2" t="inlineStr">
@@ -19394,7 +19410,7 @@
       </c>
       <c r="AD153" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -19514,7 +19530,7 @@
       </c>
       <c r="AD154" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -19584,7 +19600,7 @@
       </c>
       <c r="P155" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q155" s="2" t="inlineStr">
@@ -19628,17 +19644,17 @@
       </c>
       <c r="AB155" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC155" s="2" t="inlineStr">
         <is>
-          <t>139.3</t>
+          <t>137.5</t>
         </is>
       </c>
       <c r="AD155" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -19762,7 +19778,7 @@
       </c>
       <c r="AD156" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -19832,7 +19848,7 @@
       </c>
       <c r="P157" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q157" s="2" t="inlineStr">
@@ -19886,7 +19902,7 @@
       </c>
       <c r="AD157" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -20010,7 +20026,7 @@
       </c>
       <c r="AD158" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -20382,7 +20398,7 @@
       </c>
       <c r="AD161" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -20506,7 +20522,7 @@
       </c>
       <c r="AD162" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -20630,7 +20646,7 @@
       </c>
       <c r="AD163" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -20956,7 +20972,7 @@
       </c>
       <c r="P166" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q166" s="2" t="inlineStr">
@@ -21000,12 +21016,12 @@
       </c>
       <c r="AB166" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC166" s="2" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>142.0</t>
         </is>
       </c>
       <c r="AD166" s="2" t="inlineStr">
@@ -21076,7 +21092,7 @@
       </c>
       <c r="P167" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q167" s="2" t="inlineStr">
@@ -21250,7 +21266,7 @@
       </c>
       <c r="AD168" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -21320,7 +21336,7 @@
       </c>
       <c r="P169" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q169" s="2" t="inlineStr">
@@ -21364,17 +21380,17 @@
       </c>
       <c r="AB169" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC169" s="2" t="inlineStr">
         <is>
-          <t>138.7</t>
+          <t>135.8</t>
         </is>
       </c>
       <c r="AD169" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -21444,7 +21460,7 @@
       </c>
       <c r="P170" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q170" s="2" t="inlineStr">
@@ -21488,12 +21504,12 @@
       </c>
       <c r="AB170" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC170" s="2" t="inlineStr">
         <is>
-          <t>157.5</t>
+          <t>150.0</t>
         </is>
       </c>
       <c r="AD170" s="2" t="inlineStr">
@@ -21568,7 +21584,7 @@
       </c>
       <c r="P171" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q171" s="2" t="inlineStr">
@@ -21622,7 +21638,7 @@
       </c>
       <c r="AD171" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -21692,7 +21708,7 @@
       </c>
       <c r="P172" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q172" s="2" t="inlineStr">
@@ -21746,7 +21762,7 @@
       </c>
       <c r="AD172" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -21816,7 +21832,7 @@
       </c>
       <c r="P173" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q173" s="2" t="inlineStr">
@@ -21870,7 +21886,7 @@
       </c>
       <c r="AD173" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -21940,7 +21956,7 @@
       </c>
       <c r="P174" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q174" s="2" t="inlineStr">
@@ -21984,17 +22000,17 @@
       </c>
       <c r="AB174" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC174" s="2" t="inlineStr">
         <is>
-          <t>148.0</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AD174" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -22064,7 +22080,7 @@
       </c>
       <c r="P175" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q175" s="2" t="inlineStr">
@@ -22118,7 +22134,7 @@
       </c>
       <c r="AD175" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -22188,7 +22204,7 @@
       </c>
       <c r="P176" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q176" s="2" t="inlineStr">
@@ -22366,7 +22382,7 @@
       </c>
       <c r="AD177" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -22436,7 +22452,7 @@
       </c>
       <c r="P178" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q178" s="2" t="inlineStr">
@@ -22734,7 +22750,7 @@
       </c>
       <c r="AD180" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -22854,7 +22870,7 @@
       </c>
       <c r="AD181" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -22978,7 +22994,7 @@
       </c>
       <c r="AD182" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -23048,7 +23064,7 @@
       </c>
       <c r="P183" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q183" s="2" t="inlineStr">
@@ -23102,7 +23118,7 @@
       </c>
       <c r="AD183" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -23226,7 +23242,7 @@
       </c>
       <c r="AD184" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -23350,7 +23366,7 @@
       </c>
       <c r="AD185" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -23503,32 +23519,36 @@
       </c>
       <c r="G187" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H187" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I187" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:47</t>
         </is>
       </c>
       <c r="J187" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>147分钟</t>
         </is>
       </c>
       <c r="K187" s="2" t="inlineStr"/>
       <c r="L187" s="2" t="inlineStr"/>
       <c r="M187" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N187" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N187" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O187" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -23536,7 +23556,7 @@
       </c>
       <c r="P187" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q187" s="2" t="inlineStr">
@@ -23560,17 +23580,17 @@
       </c>
       <c r="X187" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y187" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z187" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA187" s="2" t="inlineStr">
@@ -23580,17 +23600,17 @@
       </c>
       <c r="AB187" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC187" s="2" t="inlineStr">
         <is>
-          <t>141.5</t>
+          <t>143.3</t>
         </is>
       </c>
       <c r="AD187" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -23714,7 +23734,7 @@
       </c>
       <c r="AD188" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -23747,32 +23767,36 @@
       </c>
       <c r="G189" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H189" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I189" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="J189" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="K189" s="2" t="inlineStr"/>
       <c r="L189" s="2" t="inlineStr"/>
       <c r="M189" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N189" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N189" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O189" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -23780,7 +23804,7 @@
       </c>
       <c r="P189" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q189" s="2" t="inlineStr">
@@ -23804,17 +23828,17 @@
       </c>
       <c r="X189" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y189" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z189" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA189" s="2" t="inlineStr">
@@ -23824,17 +23848,17 @@
       </c>
       <c r="AB189" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC189" s="2" t="inlineStr">
         <is>
-          <t>139.3</t>
+          <t>137.5</t>
         </is>
       </c>
       <c r="AD189" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -23867,32 +23891,36 @@
       </c>
       <c r="G190" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H190" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I190" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:57</t>
         </is>
       </c>
       <c r="J190" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="K190" s="2" t="inlineStr"/>
       <c r="L190" s="2" t="inlineStr"/>
       <c r="M190" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N190" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N190" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O190" s="2" t="inlineStr">
         <is>
           <t>05:49</t>
@@ -23900,7 +23928,7 @@
       </c>
       <c r="P190" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q190" s="2" t="inlineStr">
@@ -23924,17 +23952,17 @@
       </c>
       <c r="X190" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y190" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z190" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA190" s="2" t="inlineStr">
@@ -23944,17 +23972,17 @@
       </c>
       <c r="AB190" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC190" s="2" t="inlineStr">
         <is>
-          <t>138.7</t>
+          <t>135.8</t>
         </is>
       </c>
       <c r="AD190" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -23987,32 +24015,36 @@
       </c>
       <c r="G191" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H191" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I191" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="J191" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>140分钟</t>
         </is>
       </c>
       <c r="K191" s="2" t="inlineStr"/>
       <c r="L191" s="2" t="inlineStr"/>
       <c r="M191" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N191" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N191" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O191" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -24020,7 +24052,7 @@
       </c>
       <c r="P191" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q191" s="2" t="inlineStr">
@@ -24044,17 +24076,17 @@
       </c>
       <c r="X191" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y191" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z191" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA191" s="2" t="inlineStr">
@@ -24064,12 +24096,12 @@
       </c>
       <c r="AB191" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC191" s="2" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>142.0</t>
         </is>
       </c>
       <c r="AD191" s="2" t="inlineStr">
@@ -24107,12 +24139,12 @@
       </c>
       <c r="G192" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="H192" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程49%处后消失；随后反向物理轨迹由seq28推进至seq60，推进32站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I192" s="2" t="inlineStr">
@@ -24140,7 +24172,7 @@
       </c>
       <c r="P192" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q192" s="2" t="inlineStr">
@@ -24148,10 +24180,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R192" s="2" t="inlineStr"/>
-      <c r="S192" s="2" t="inlineStr"/>
-      <c r="T192" s="2" t="inlineStr"/>
-      <c r="U192" s="2" t="inlineStr"/>
+      <c r="R192" s="2" t="inlineStr">
+        <is>
+          <t>物理seq32（站名待映射）</t>
+        </is>
+      </c>
+      <c r="S192" s="2" t="inlineStr">
+        <is>
+          <t>20:12</t>
+        </is>
+      </c>
+      <c r="T192" s="2" t="inlineStr">
+        <is>
+          <t>20:16</t>
+        </is>
+      </c>
+      <c r="U192" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq32映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±5分钟；反向位置物理seq28（站名待映射） ETA 0分钟参与校验</t>
+        </is>
+      </c>
       <c r="V192" s="2" t="inlineStr">
         <is>
           <t>19:10</t>
@@ -24194,7 +24242,7 @@
       </c>
       <c r="AD192" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -24227,32 +24275,36 @@
       </c>
       <c r="G193" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H193" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I193" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:25</t>
         </is>
       </c>
       <c r="J193" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="K193" s="2" t="inlineStr"/>
       <c r="L193" s="2" t="inlineStr"/>
       <c r="M193" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N193" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N193" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O193" s="2" t="inlineStr">
         <is>
           <t>05:49</t>
@@ -24260,7 +24312,7 @@
       </c>
       <c r="P193" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q193" s="2" t="inlineStr">
@@ -24284,17 +24336,17 @@
       </c>
       <c r="X193" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y193" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z193" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA193" s="2" t="inlineStr">
@@ -24304,17 +24356,17 @@
       </c>
       <c r="AB193" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC193" s="2" t="inlineStr">
         <is>
-          <t>148.0</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AD193" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -24347,32 +24399,36 @@
       </c>
       <c r="G194" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H194" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I194" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:35</t>
         </is>
       </c>
       <c r="J194" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>135分钟</t>
         </is>
       </c>
       <c r="K194" s="2" t="inlineStr"/>
       <c r="L194" s="2" t="inlineStr"/>
       <c r="M194" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N194" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N194" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O194" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -24380,7 +24436,7 @@
       </c>
       <c r="P194" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q194" s="2" t="inlineStr">
@@ -24404,17 +24460,17 @@
       </c>
       <c r="X194" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y194" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z194" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA194" s="2" t="inlineStr">
@@ -24424,12 +24480,12 @@
       </c>
       <c r="AB194" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC194" s="2" t="inlineStr">
         <is>
-          <t>157.5</t>
+          <t>150.0</t>
         </is>
       </c>
       <c r="AD194" s="2" t="inlineStr">
@@ -24467,12 +24523,12 @@
       </c>
       <c r="G195" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="H195" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程5%处后消失；随后反向物理轨迹由seq30推进至seq52，推进22站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I195" s="2" t="inlineStr">
@@ -24500,7 +24556,7 @@
       </c>
       <c r="P195" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q195" s="2" t="inlineStr">
@@ -24554,7 +24610,7 @@
       </c>
       <c r="AD195" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -24620,7 +24676,7 @@
       </c>
       <c r="P196" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q196" s="2" t="inlineStr">
@@ -24674,7 +24730,7 @@
       </c>
       <c r="AD196" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -24740,7 +24796,7 @@
       </c>
       <c r="P197" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q197" s="2" t="inlineStr">
@@ -24860,7 +24916,7 @@
       </c>
       <c r="P198" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q198" s="2" t="inlineStr">
@@ -24914,7 +24970,7 @@
       </c>
       <c r="AD198" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -24980,7 +25036,7 @@
       </c>
       <c r="P199" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q199" s="2" t="inlineStr">
@@ -25034,7 +25090,7 @@
       </c>
       <c r="AD199" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -25100,7 +25156,7 @@
       </c>
       <c r="P200" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q200" s="2" t="inlineStr">
@@ -25220,7 +25276,7 @@
       </c>
       <c r="P201" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q201" s="2" t="inlineStr">
@@ -25274,7 +25330,7 @@
       </c>
       <c r="AD201" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -25340,7 +25396,7 @@
       </c>
       <c r="P202" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q202" s="2" t="inlineStr">
@@ -25384,17 +25440,17 @@
       </c>
       <c r="AB202" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC202" s="2" t="inlineStr">
         <is>
-          <t>141.5</t>
+          <t>143.3</t>
         </is>
       </c>
       <c r="AD202" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -25580,7 +25636,7 @@
       </c>
       <c r="P204" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q204" s="2" t="inlineStr">
@@ -25624,12 +25680,12 @@
       </c>
       <c r="AB204" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC204" s="2" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="AD204" s="2" t="inlineStr">
@@ -26002,7 +26058,7 @@
       </c>
       <c r="AD207" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -26072,7 +26128,7 @@
       </c>
       <c r="P208" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q208" s="2" t="inlineStr">
@@ -26116,17 +26172,17 @@
       </c>
       <c r="AB208" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC208" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>86.4</t>
         </is>
       </c>
       <c r="AD208" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -26196,7 +26252,7 @@
       </c>
       <c r="P209" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="Q209" s="2" t="inlineStr">
@@ -26245,7 +26301,7 @@
       </c>
       <c r="AC209" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>87.8</t>
         </is>
       </c>
       <c r="AD209" s="2" t="inlineStr">
@@ -26564,7 +26620,7 @@
       </c>
       <c r="P212" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q212" s="2" t="inlineStr">
@@ -26613,7 +26669,7 @@
       </c>
       <c r="AC212" s="2" t="inlineStr">
         <is>
-          <t>92.2</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AD212" s="2" t="inlineStr">
@@ -26688,7 +26744,7 @@
       </c>
       <c r="P213" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q213" s="2" t="inlineStr">
@@ -26732,12 +26788,12 @@
       </c>
       <c r="AB213" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC213" s="2" t="inlineStr">
         <is>
-          <t>89.5</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AD213" s="2" t="inlineStr">
@@ -27428,7 +27484,7 @@
       </c>
       <c r="P219" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q219" s="2" t="inlineStr">
@@ -27472,12 +27528,12 @@
       </c>
       <c r="AB219" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC219" s="2" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AD219" s="2" t="inlineStr">
@@ -27552,7 +27608,7 @@
       </c>
       <c r="P220" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q220" s="2" t="inlineStr">
@@ -27596,12 +27652,12 @@
       </c>
       <c r="AB220" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC220" s="2" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="AD220" s="2" t="inlineStr">
@@ -27978,7 +28034,7 @@
       </c>
       <c r="AD223" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -28044,7 +28100,7 @@
       </c>
       <c r="P224" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="Q224" s="2" t="inlineStr">
@@ -28093,7 +28149,7 @@
       </c>
       <c r="AC224" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>87.8</t>
         </is>
       </c>
       <c r="AD224" s="2" t="inlineStr">
@@ -28284,7 +28340,7 @@
       </c>
       <c r="P226" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q226" s="2" t="inlineStr">
@@ -28328,17 +28384,17 @@
       </c>
       <c r="AB226" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC226" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>86.4</t>
         </is>
       </c>
       <c r="AD226" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -28462,7 +28518,7 @@
       </c>
       <c r="AD227" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -28780,7 +28836,7 @@
       </c>
       <c r="P230" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q230" s="2" t="inlineStr">
@@ -28824,12 +28880,12 @@
       </c>
       <c r="AB230" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC230" s="2" t="inlineStr">
         <is>
-          <t>89.5</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AD230" s="2" t="inlineStr">
@@ -28900,7 +28956,7 @@
       </c>
       <c r="P231" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q231" s="2" t="inlineStr">
@@ -28949,7 +29005,7 @@
       </c>
       <c r="AC231" s="2" t="inlineStr">
         <is>
-          <t>92.2</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AD231" s="2" t="inlineStr">
@@ -29516,7 +29572,7 @@
       </c>
       <c r="P236" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q236" s="2" t="inlineStr">
@@ -29560,12 +29616,12 @@
       </c>
       <c r="AB236" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC236" s="2" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AD236" s="2" t="inlineStr">
@@ -29818,7 +29874,7 @@
       </c>
       <c r="AD238" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -30008,7 +30064,7 @@
       </c>
       <c r="P240" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="Q240" s="2" t="inlineStr">
@@ -30069,7 +30125,7 @@
       </c>
       <c r="AC240" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>87.8</t>
         </is>
       </c>
       <c r="AD240" s="2" t="inlineStr">
@@ -30388,7 +30444,7 @@
       </c>
       <c r="P243" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q243" s="2" t="inlineStr">
@@ -30444,12 +30500,12 @@
       </c>
       <c r="AB243" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC243" s="2" t="inlineStr">
         <is>
-          <t>89.5</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AD243" s="2" t="inlineStr">
@@ -31198,7 +31254,7 @@
       </c>
       <c r="AD249" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -32314,7 +32370,7 @@
       </c>
       <c r="AD258" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -32508,7 +32564,7 @@
       </c>
       <c r="P260" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q260" s="2" t="inlineStr">
@@ -32552,12 +32608,12 @@
       </c>
       <c r="AB260" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC260" s="2" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="AD260" s="2" t="inlineStr">
@@ -33128,7 +33184,7 @@
       </c>
       <c r="P265" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q265" s="2" t="inlineStr">
@@ -33172,17 +33228,17 @@
       </c>
       <c r="AB265" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC265" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>86.4</t>
         </is>
       </c>
       <c r="AD265" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -33376,7 +33432,7 @@
       </c>
       <c r="P267" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q267" s="2" t="inlineStr">
@@ -33425,7 +33481,7 @@
       </c>
       <c r="AC267" s="2" t="inlineStr">
         <is>
-          <t>92.2</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AD267" s="2" t="inlineStr">
@@ -33868,7 +33924,7 @@
       </c>
       <c r="P271" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="Q271" s="2" t="inlineStr">
@@ -33917,7 +33973,7 @@
       </c>
       <c r="AC271" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>87.8</t>
         </is>
       </c>
       <c r="AD271" s="2" t="inlineStr">
@@ -33992,7 +34048,7 @@
       </c>
       <c r="P272" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q272" s="2" t="inlineStr">
@@ -34036,12 +34092,12 @@
       </c>
       <c r="AB272" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC272" s="2" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AD272" s="2" t="inlineStr">
@@ -34240,7 +34296,7 @@
       </c>
       <c r="P274" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q274" s="2" t="inlineStr">
@@ -34284,12 +34340,12 @@
       </c>
       <c r="AB274" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC274" s="2" t="inlineStr">
         <is>
-          <t>89.5</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AD274" s="2" t="inlineStr">
@@ -34418,7 +34474,7 @@
       </c>
       <c r="AD275" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -34736,7 +34792,7 @@
       </c>
       <c r="P278" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q278" s="2" t="inlineStr">
@@ -34780,12 +34836,12 @@
       </c>
       <c r="AB278" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC278" s="2" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="AD278" s="2" t="inlineStr">
@@ -35348,7 +35404,7 @@
       </c>
       <c r="P283" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q283" s="2" t="inlineStr">
@@ -35392,17 +35448,17 @@
       </c>
       <c r="AB283" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC283" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>86.4</t>
         </is>
       </c>
       <c r="AD283" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -35592,7 +35648,7 @@
       </c>
       <c r="P285" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q285" s="2" t="inlineStr">
@@ -35641,7 +35697,7 @@
       </c>
       <c r="AC285" s="2" t="inlineStr">
         <is>
-          <t>92.2</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AD285" s="2" t="inlineStr">
@@ -35960,7 +36016,7 @@
       </c>
       <c r="P288" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q288" s="2" t="inlineStr">
@@ -36004,12 +36060,12 @@
       </c>
       <c r="AB288" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC288" s="2" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AD288" s="2" t="inlineStr">
@@ -36084,7 +36140,7 @@
       </c>
       <c r="P289" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="Q289" s="2" t="inlineStr">
@@ -36133,7 +36189,7 @@
       </c>
       <c r="AC289" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>87.8</t>
         </is>
       </c>
       <c r="AD289" s="2" t="inlineStr">
@@ -36386,7 +36442,7 @@
       </c>
       <c r="AD291" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -36580,7 +36636,7 @@
       </c>
       <c r="P293" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q293" s="2" t="inlineStr">
@@ -36624,12 +36680,12 @@
       </c>
       <c r="AB293" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC293" s="2" t="inlineStr">
         <is>
-          <t>89.5</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AD293" s="2" t="inlineStr">
@@ -36952,7 +37008,7 @@
       </c>
       <c r="P296" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q296" s="2" t="inlineStr">
@@ -36996,12 +37052,12 @@
       </c>
       <c r="AB296" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC296" s="2" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="AD296" s="2" t="inlineStr">
@@ -37448,7 +37504,7 @@
       </c>
       <c r="P300" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q300" s="2" t="inlineStr">
@@ -37492,17 +37548,17 @@
       </c>
       <c r="AB300" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC300" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>86.4</t>
         </is>
       </c>
       <c r="AD300" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -37545,24 +37601,24 @@
       </c>
       <c r="I301" s="2" t="inlineStr">
         <is>
-          <t>20:46</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="J301" s="2" t="inlineStr">
         <is>
-          <t>81分钟</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="K301" s="2" t="inlineStr"/>
       <c r="L301" s="2" t="inlineStr"/>
       <c r="M301" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="N301" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O301" s="2" t="inlineStr">
@@ -37572,7 +37628,7 @@
       </c>
       <c r="P301" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="Q301" s="2" t="inlineStr">
@@ -37621,7 +37677,7 @@
       </c>
       <c r="AC301" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>87.8</t>
         </is>
       </c>
       <c r="AD301" s="2" t="inlineStr">
@@ -37669,24 +37725,24 @@
       </c>
       <c r="I302" s="2" t="inlineStr">
         <is>
-          <t>20:57</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="J302" s="2" t="inlineStr">
         <is>
-          <t>87分钟</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="K302" s="2" t="inlineStr"/>
       <c r="L302" s="2" t="inlineStr"/>
       <c r="M302" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
         </is>
       </c>
       <c r="N302" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O302" s="2" t="inlineStr">
@@ -37696,7 +37752,7 @@
       </c>
       <c r="P302" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q302" s="2" t="inlineStr">
@@ -37745,7 +37801,7 @@
       </c>
       <c r="AC302" s="2" t="inlineStr">
         <is>
-          <t>92.2</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AD302" s="2" t="inlineStr">
@@ -37783,32 +37839,36 @@
       </c>
       <c r="G303" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H303" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I303" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:17</t>
         </is>
       </c>
       <c r="J303" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="K303" s="2" t="inlineStr"/>
       <c r="L303" s="2" t="inlineStr"/>
       <c r="M303" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N303" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N303" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O303" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -37816,7 +37876,7 @@
       </c>
       <c r="P303" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q303" s="2" t="inlineStr">
@@ -37840,17 +37900,17 @@
       </c>
       <c r="X303" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y303" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z303" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA303" s="2" t="inlineStr">
@@ -37860,12 +37920,12 @@
       </c>
       <c r="AB303" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC303" s="2" t="inlineStr">
         <is>
-          <t>89.5</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AD303" s="2" t="inlineStr">
@@ -37903,32 +37963,36 @@
       </c>
       <c r="G304" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H304" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I304" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="J304" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="K304" s="2" t="inlineStr"/>
       <c r="L304" s="2" t="inlineStr"/>
       <c r="M304" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N304" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N304" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O304" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -37936,7 +38000,7 @@
       </c>
       <c r="P304" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q304" s="2" t="inlineStr">
@@ -37960,17 +38024,17 @@
       </c>
       <c r="X304" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y304" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z304" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA304" s="2" t="inlineStr">
@@ -37980,12 +38044,12 @@
       </c>
       <c r="AB304" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC304" s="2" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AD304" s="2" t="inlineStr">
@@ -38023,32 +38087,36 @@
       </c>
       <c r="G305" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H305" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I305" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:40</t>
         </is>
       </c>
       <c r="J305" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="K305" s="2" t="inlineStr"/>
       <c r="L305" s="2" t="inlineStr"/>
       <c r="M305" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N305" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N305" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O305" s="2" t="inlineStr">
         <is>
           <t>05:48</t>
@@ -38056,7 +38124,7 @@
       </c>
       <c r="P305" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q305" s="2" t="inlineStr">
@@ -38080,17 +38148,17 @@
       </c>
       <c r="X305" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y305" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z305" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA305" s="2" t="inlineStr">
@@ -38100,12 +38168,12 @@
       </c>
       <c r="AB305" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC305" s="2" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="AD305" s="2" t="inlineStr">
@@ -38143,32 +38211,36 @@
       </c>
       <c r="G306" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H306" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I306" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:56</t>
         </is>
       </c>
       <c r="J306" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="K306" s="2" t="inlineStr"/>
       <c r="L306" s="2" t="inlineStr"/>
       <c r="M306" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N306" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="N306" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="O306" s="2" t="inlineStr">
         <is>
           <t>06:20</t>
@@ -38176,7 +38248,7 @@
       </c>
       <c r="P306" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q306" s="2" t="inlineStr">
@@ -38200,17 +38272,17 @@
       </c>
       <c r="X306" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y306" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z306" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA306" s="2" t="inlineStr">
@@ -38220,17 +38292,17 @@
       </c>
       <c r="AB306" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC306" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>86.4</t>
         </is>
       </c>
       <c r="AD306" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -38296,7 +38368,7 @@
       </c>
       <c r="P307" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q307" s="2" t="inlineStr">
@@ -38345,7 +38417,7 @@
       </c>
       <c r="AC307" s="2" t="inlineStr">
         <is>
-          <t>92.2</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AD307" s="2" t="inlineStr">
@@ -38416,7 +38488,7 @@
       </c>
       <c r="P308" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q308" s="2" t="inlineStr">
@@ -38460,12 +38532,12 @@
       </c>
       <c r="AB308" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC308" s="2" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AD308" s="2" t="inlineStr">
